--- a/dados/oferta-diesel.xlsx
+++ b/dados/oferta-diesel.xlsx
@@ -1,23 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="LEIA-ME" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Balanço anual" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Balanço mensal" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Vendas por tipo" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Produção por refinaria" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEIA-ME" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balanço anual" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balanço mensal" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vendas por tipo" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produção por refinaria" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Importação por agente" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Importação por empresa" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Balanço anual'!$A$1:$J$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Balanço mensal'!$A$1:$N$321</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Vendas por tipo'!$A$1:$G$165</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Produção por refinaria'!$A$1:$W$441</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Importação por agente'!$A$1:$I$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Importação por empresa'!$A$1:$W$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -438,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -460,7 +464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
     </row>
@@ -537,182 +541,311 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Importação por agente</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Quem traz o diesel de fora, por tipo de agente, desde 2020</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Importação por empresa</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>As 20 maiores importadoras em coluna, desde 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>ÓLEO DIESEL E BIODIESEL SÃO PRODUTOS DIFERENTES, e esta planilha nunca soma um no outro.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Óleo diesel A</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>O mineral: o que sai da refinaria ou vem importado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Biodiesel (B100)</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Feito de óleo vegetal e gordura animal. Outro produto, e todo nacional.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Óleo diesel B</t>
+          <t>Óleo diesel A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>O que a distribuidora vende: diesel A com biodiesel misturado na proporção que a lei manda (B15 desde 8/2025).</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t>O mineral: o que sai da refinaria ou vem importado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Biodiesel (B100)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Feito de óleo vegetal e gordura animal. Outro produto, e todo nacional.</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O biodiesel entra aqui por uma razão só: sem ele as duas pontas não fecham. A ANP mede VENDAS em diesel B e mede</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>PRODUÇÃO e IMPORTAÇÃO em diesel A. Em 2025 foram 69,5 milhões de m³ vendidos contra 63,7 milhões de oferta de diesel A</t>
-        </is>
-      </c>
-    </row>
+          <t>Óleo diesel B</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>O que a distribuidora vende: diesel A com biodiesel misturado na proporção que a lei manda (B15 desde 8/2025).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>O biodiesel entra aqui por uma razão só: sem ele as duas pontas não fecham. A ANP mede VENDAS em diesel B e mede</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO e IMPORTAÇÃO em diesel A. Em 2025 foram 69,5 milhões de m³ vendidos contra 63,7 milhões de oferta de diesel A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>— o buraco de 5,8 milhões não existe, é biodiesel (9,8 milhões naquele ano). Cada coluna diz qual produto está medindo.</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>As contas:</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>oferta de diesel A</t>
         </is>
       </c>
-      <c r="B21">
+      <c r="B23">
         <f> produção nacional + importação − exportação</f>
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>% importado</t>
         </is>
       </c>
-      <c r="B22">
+      <c r="B24">
         <f> importação ÷ oferta de diesel A</f>
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>diesel A nas vendas</t>
         </is>
       </c>
-      <c r="B23">
+      <c r="B25">
         <f> vendas de diesel B − biodiesel misturado</f>
         <v/>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A produção nacional é de TODAS as refinarias do país, não só as da Petrobras: entram Mataripe (Acelen), Manguinhos</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>(Refit), Riograndense, 3R Potiguar e as demais. Produtores que não são refinaria reportam zero diesel à ANP; a conta</t>
-        </is>
-      </c>
-    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>A produção nacional é de TODAS as refinarias do país, não só as da Petrobras: entram Mataripe (Acelen), Manguinhos</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>(Refit), Riograndense, 3R Potiguar e as demais. Produtores que não são refinaria reportam zero diesel à ANP; a conta</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>os inclui mesmo assim, para o dia em que deixarem de reportar zero.</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>ATENÇÃO — 'vendas' é o que as DISTRIBUIDORAS venderam, não o consumo do país.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Produtor que vende direto a grande consumidor não passa por aí. É essa a maior parte da diferença entre a oferta e as</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>vendas, junto com estoque. Não há dado de estoque aqui, então o resíduo entre as duas não é variação de estoque.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>vendas, junto com estoque. Não há dado de estoque aqui, então o resíduo entre as duas não é variação de estoque.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>O biodiesel misturado só existe na série da ANP a partir de 2017. Antes disso a coluna fica vazia, e 'diesel A nas</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>vendas' também — a mistura existia (B5 desde 2010), mas o volume não está publicado nesse arquivo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>vendas' também — a mistura existia (B5 desde 2010), mas o volume não está publicado nesse arquivo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>QUEM IMPORTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>A série volumétrica de comércio exterior não diz quem trouxe a carga. Quem diz é o Relatório de Desembaraços, que a</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ANP monta do Siscomex e publica por empresa. Ele começa em JANEIRO DE 2020 — antes disso não existe dado por agente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Vem em quilos; a conversão para m³ usa 0,84 t/m³, o mesmo fator que a própria ANP aplica para montar o volumétrico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>importador de registro</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>O relatório nomeia quem registrou a importação, não o dono final da carga. Trading que</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>importa por conta de distribuidora aparece como trading.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>cobertura</t>
+        </is>
+      </c>
+      <c r="B45">
+        <f> desembaraçado ÷ importação volumétrica do mesmo mês. Alguns meses saem incompletos e</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>são completados depois; onde a cobertura foge de 100%, a abertura por agente daquele mês não</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>fecha com o total e não deve ser lida como participação.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>classificação</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>O tipo de agente é nosso, feito da razão social mais a estrutura societária conhecida. O</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>braço trading de um grupo (Vibra Trading, Royal FIC Comercial) vai com o grupo, não com as</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>tradings independentes. A aba por empresa traz o dado cru, sem classificação.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>A soma móvel de 12 meses existe porque o diesel tem sazonalidade forte (safra, chuva, feriado). Mês contra mês do</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>ano anterior também serve; mês contra mês anterior, não.</t>
         </is>
@@ -49363,4 +49496,7060 @@
   <autoFilter ref="A1:W441"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I81"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>mês</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Petrobras</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>grupo distribuidor</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>trading/importador independente</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>refinaria privada</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>central petroquímica</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>outros/uso próprio</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>total desembaraçado</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>cobertura</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2020-01</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n">
+        <v>160368.7523809524</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>85386.64285714287</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>942310.0845238094</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>1188065.479761905</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>0.9999999997995941</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2020-02</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>214189.8710714286</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>61403.89942857144</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>826613.6285714286</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>20677.84404761905</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>1122885.243119048</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>1.000000000996582</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2020-03</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>45595.38235714286</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>900222.0026523812</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>945817.3850095241</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>1.000000009314191</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2020-04</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>69160.04909523811</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>918280.0726191548</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>9706.155952380954</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>997146.2776667739</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>1.000000000267537</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2020-05</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>18994.17883333333</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>674828.6761130953</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>11352.07142857143</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>705174.926375</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>1.000000000248165</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2020-06</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>22683.76097619048</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>761412.2501666667</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>50365.32976190477</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>834461.3409047619</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>1.000000000485058</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2020-07</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>31148.12573809524</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>1063345.898452381</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>27084.49880952381</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>9937.558333333334</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>1131516.081333333</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0.9999974214602942</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2020-08</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>90785.34476190477</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>19832.33465609524</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>986089.7273809523</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>23238.79404761905</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>7979.972619047619</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>1127926.173465619</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>0.9999999986396442</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2020-09</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>60587.72380952381</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>26088.46058202381</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>898685.8702976191</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>985362.0546891667</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>1.000000002323173</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2020-10</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>158156.3222619048</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>52392.62321428572</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>946708.7341666667</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>18718.50833333334</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>1175976.187976191</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>1.00000000423154</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2020-11</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>86247.4965952381</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>751187.1785714286</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>9767.826190476191</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>4918.432142857143</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>852120.9335</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>1.000000014199863</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2020-12</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>226367.8316666667</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>172195.5985119047</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>500701.7619071429</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>14187.5880952381</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>14651.10833333333</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>928103.8885142857</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>1.000000004325255</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2021-01</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>256480.7416666667</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>57947.00119047619</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>452711.8702380952</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>23779.51309523809</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>790919.1261904762</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>0.9999999999879585</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2021-02</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>178776.148452381</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>51740.79761904763</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>471936.9130952382</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>10385.10238095238</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>712838.9615476191</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>0.9999999995056654</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2021-03</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>229285.2263095239</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>37417.75238095238</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>606833.8091666667</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>18766.49047619048</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>892303.2783333334</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>1.000000005080485</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2021-04</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>699163.0261904763</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>21096.85714285714</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>682184.5339879763</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>1402444.41732131</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>1.000000000229107</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2021-05</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>732102.1904761905</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>24869.85476190476</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>584597.3178571429</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>24193.62976190477</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>1365762.992857143</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>1.000000153655632</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>456028.4550000001</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>59745.93333333333</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>604086.1240476191</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>12642.57261904762</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>1132503.085</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>0.9063870385940503</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>465691.5839285714</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>8798.235714285714</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>745189.9044048213</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>17578.25119047619</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>1237257.975238155</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>1.000000003425441</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>834286.1533333334</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>70008.72380952381</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>762139.5714285715</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>5865.033333333333</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>1672299.481904762</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>0.9999999999430497</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2021-09</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>406162.4036904762</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>15966.35476190476</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>540338.1964285714</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>12189.55</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>974656.5048809523</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>1.000000000083057</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2021-10</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>1203351.686666667</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>15926.91821428572</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>621906.3410714286</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>11893.09642857143</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>1853078.042380952</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>1.000000009919146</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>549028.1927380953</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>173471.2916666667</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>401778.2555419286</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>11042.87261904762</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>1135320.612565738</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>1.000000049823583</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>342594.730952381</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>324819.4940476191</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>482975.8328690476</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>1150390.057869048</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>1.000075784274156</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2022-01</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>474941.335</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>322199.9928571429</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>578122.2202380951</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>19835.11904761905</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>1395098.667142857</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>1.000000002252785</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2022-02</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>125071.8772619048</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>169825.248797619</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>247448.7130972262</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>19689.13214285714</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>562034.9712996072</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>0.9999999998213761</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2022-03</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>474604.3251190477</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>302949.5892857143</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>414779.5708928572</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>1192333.485297619</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>1.000000001926994</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>712839.0233333333</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>397909.0908333334</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>435133.8726190476</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>11706.58690476191</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>1557588.573690476</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>0.9999950806830765</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2022-05</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>566619.5333333333</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>376530.7976190476</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>500144.9110285715</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>4878.003571428571</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>0.02380952380952381</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>1448173.269361905</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>1.000000016822507</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>306643.3928571428</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>345034.4174976191</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>287133.6119047619</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>4984.442857142857</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>943795.8651166667</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>0.9832897164399287</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2022-07</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>575861.3809523811</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>426249.6726190477</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>330058.3860357143</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>4984.442857142857</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>1337153.882464286</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>1.000000638269717</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>953034.4201190476</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>398433.1904761905</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>462753.4642857143</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>32611.40476190476</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>1846832.479642857</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>1.000016714650168</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2022-09</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>1113585.639285714</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>366156.6464285714</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>519055.5011906547</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>1998797.78690494</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>1.0001497133434</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>760279.9927690477</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>343427.3428571428</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>249828.6178335119</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>70071.79404761906</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>35700.62976190476</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>1459308.377269226</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>1.000053074717433</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>150721.9130952381</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>296020.1952380952</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>212218.8970476191</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>20409.4369047619</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>679370.4422857143</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>1.000000127008359</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2022-12</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>708122.8333333334</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>299177.4023809524</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>428713.6403227976</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>19615.68571428572</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>1455629.561751369</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>0.9731919170260969</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>298002.2035714285</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>164448.8523809524</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>224902.2297619047</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>50309.33214285714</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>4125.790476190477</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>741788.4083333333</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>1.000000000044936</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>483274.4595238095</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>187090.0821428571</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>318368.7547619048</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>37267.51904761905</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>4125.790476190477</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>1030126.605952381</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>0.9999999999537735</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>643456.6047619048</v>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>284646.3166666667</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>764333.2264047619</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>21844.80119047619</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>4125.790476190477</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>1718406.7395</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>1.000000000290967</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>116297.8690476191</v>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>225997.0607142857</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>545893.4773809523</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>12321.14166666667</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>31885.30238095238</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>932394.8511904762</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>0.9999999999897856</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>499050.8892857143</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>130812.2928571429</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>547469.0523809524</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>131649.144047619</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>54131.38333333333</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>1363112.761904762</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>0.9999999999301318</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>230819.8583333333</v>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>197664.0892857143</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>533980.0166666666</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>117576.3928571429</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>1080040.357142857</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>1.00000000013227</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>470739.6566666667</v>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>145758.8404761905</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>355249.5623571429</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>44535.77380952381</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>52545.59642857143</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>1068829.429738095</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>1.00743388610444</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>240317.9847738096</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>61048.71666666667</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>788354.1273809524</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>162619.6678571429</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>55888.44642857143</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>1308228.943107143</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>0.9964376505332136</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="n">
+        <v>274184.6963095238</v>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>40795.13095238095</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>577329.3902976192</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>86731.125</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>156289.2547619048</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>1135329.597321429</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>1.000000117429727</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="n">
+        <v>248903.1702380952</v>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>176135.8226190476</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>1010612.342144048</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>55702.64761904762</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>1491353.982620238</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>1.225878838252057</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>271309.7666666667</v>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>119299.9345238095</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>539428.6840533928</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>90924.21666666666</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>4972.807142857144</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>1025935.409053393</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>1.000000043914456</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>131636.7976190476</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>221402.4892857143</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>1206650.224488167</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>196927.3642857143</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>121571.1187988095</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>1878187.994477453</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>0.9999050395461339</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>189232.4571428572</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>195836.080952381</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>437675.6660952381</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>165369.6416666667</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>58682.49761904762</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>1046796.34347619</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>1.000000066370307</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>243694.1404761905</v>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>125490.9797619048</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>316041.0797619048</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>172000.2523809524</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>857226.4523809524</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>0.9999999999777801</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>475145.7785714286</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>175834.5047619048</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>392289.8374040714</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>195845.2</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>1239115.320737405</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>1.000000055472971</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n">
+        <v>353917.455952381</v>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>194120.0833333333</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>469439.6547619047</v>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>153290.6523809524</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>1170767.846428572</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>0.9888204097081713</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>298158.4535714285</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>657279.8869047619</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>113534.8976190476</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>1068973.238095238</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>1.000000000089093</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="n">
+        <v>409174.4238095239</v>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>495518.939657143</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>496852.803116857</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>112677.6916666667</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>1514223.858250191</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>1.000000002806844</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="n">
+        <v>267992.0480952381</v>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>357586.8994761905</v>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>388612.2928571429</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>223969.5726190476</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>9854.535714285714</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>1248015.348761905</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>1.000000032661382</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="n">
+        <v>363857.5083333334</v>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>258968.0845238095</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>353085.7702380953</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>290286.2309523809</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>1266197.594047619</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>1.00000589093803</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="n">
+        <v>432480.9369047619</v>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>273613.9476190477</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>615521.2507142858</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>274072.5857142857</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>1595688.720952381</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>1.000000004983667</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="n">
+        <v>239263.0036666667</v>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>410619.6277738095</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>516583.2738097024</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>317788.1678571429</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>5209.041666666667</v>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>1489463.114773988</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>1.000000002533791</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>342301.6472142857</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>313081.7738927738</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>179063.0869047619</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>834446.5080118214</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>1.000000073835561</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="n">
+        <v>243329.3203333333</v>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>240693.9333333334</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>252831.6324257143</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>238200.9095238096</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="4" t="n">
+        <v>975055.7956161906</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>1.000000043091065</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="n">
+        <v>371363.1952380952</v>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>372455.344047619</v>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>243943.1864628572</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>254275.2261904762</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>1242036.951939048</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>0.9976215882318978</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="n">
+        <v>566755.4952380953</v>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>181863.705952381</v>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>138695.5607142857</v>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>186283.0428571429</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="4" t="n">
+        <v>1073597.804761905</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>1.00011262912309</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="n">
+        <v>362206.99</v>
+      </c>
+      <c r="C64" s="4" t="n">
+        <v>409488.3773809525</v>
+      </c>
+      <c r="D64" s="4" t="n">
+        <v>273342.5424761904</v>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>223945.530952381</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>3202.914285714286</v>
+      </c>
+      <c r="H64" s="4" t="n">
+        <v>1272186.355095238</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>0.9810696524627497</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="n">
+        <v>325828.0083333334</v>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>615724.1440476192</v>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>406177.275</v>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>96510.67142857144</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>4896.858333333334</v>
+      </c>
+      <c r="H65" s="4" t="n">
+        <v>1449136.957142857</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>0.994912790794257</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="n">
+        <v>490249.5333333334</v>
+      </c>
+      <c r="C66" s="4" t="n">
+        <v>389654.5654761904</v>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>305848.2830952381</v>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>269534.080952381</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>3751.422857142858</v>
+      </c>
+      <c r="H66" s="4" t="n">
+        <v>1459037.885714286</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>1.000000003231092</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="n">
+        <v>406775.655952381</v>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>444032.2078928572</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>245296.4372380952</v>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>188151.2321428572</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="4" t="n">
+        <v>8675.495238095238</v>
+      </c>
+      <c r="H67" s="4" t="n">
+        <v>1292931.028464286</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>1.000000002679405</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="n">
+        <v>612398.0928571428</v>
+      </c>
+      <c r="C68" s="4" t="n">
+        <v>516727.1630952381</v>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>260667.0523809523</v>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>338153.2583333334</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>1727945.566666667</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>1.000004874405702</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="n">
+        <v>289801.5523809524</v>
+      </c>
+      <c r="C69" s="4" t="n">
+        <v>341910.5869047619</v>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>204517.9273810239</v>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>325759.4773809524</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="4" t="n">
+        <v>11262.77619047619</v>
+      </c>
+      <c r="H69" s="4" t="n">
+        <v>1173252.320238167</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>0.9072872322218014</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="n">
+        <v>909605.5701452382</v>
+      </c>
+      <c r="C70" s="4" t="n">
+        <v>375834.9790130953</v>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>196584.9880952381</v>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>259201.3785714286</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>6816.142857142857</v>
+      </c>
+      <c r="H70" s="4" t="n">
+        <v>1748043.058682143</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>0.9999999992460957</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="n">
+        <v>816819.4821738095</v>
+      </c>
+      <c r="C71" s="4" t="n">
+        <v>335159.9666666667</v>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>308096.3092857143</v>
+      </c>
+      <c r="E71" s="4" t="n">
+        <v>136143.9190476191</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>3049.954761904762</v>
+      </c>
+      <c r="H71" s="4" t="n">
+        <v>1599269.631935714</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>0.9999738518321373</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="n">
+        <v>647712.8000785715</v>
+      </c>
+      <c r="C72" s="4" t="n">
+        <v>256271.3607142858</v>
+      </c>
+      <c r="D72" s="4" t="n">
+        <v>339014.6211809524</v>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>122150.6809523809</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="4" t="n">
+        <v>1365149.462926191</v>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>0.9964023644979294</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="n">
+        <v>272975.4964285714</v>
+      </c>
+      <c r="C73" s="4" t="n">
+        <v>379101.419047619</v>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>353450.5289049047</v>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>169936.1083333333</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>14787.32380952381</v>
+      </c>
+      <c r="H73" s="4" t="n">
+        <v>1190250.876523952</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>0.7777702622028692</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="n">
+        <v>698974.5143904762</v>
+      </c>
+      <c r="C74" s="4" t="n">
+        <v>222238.0238095238</v>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>295208.6023809523</v>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>99802.63452380952</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>6395.849999999999</v>
+      </c>
+      <c r="H74" s="4" t="n">
+        <v>1322619.625104762</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>1.000000000079208</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="n">
+        <v>405139.0345238096</v>
+      </c>
+      <c r="C75" s="4" t="n">
+        <v>382492.8916666667</v>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>489837.5959476191</v>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>102280.8964285714</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>1278.616666666667</v>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>1381029.035233333</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>1.000025134957277</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="n">
+        <v>246962.2702380953</v>
+      </c>
+      <c r="C76" s="4" t="n">
+        <v>299024.2607142857</v>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>435800.5750000476</v>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>45174.81666666667</v>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>12804.99880952381</v>
+      </c>
+      <c r="H76" s="4" t="n">
+        <v>1039766.921428619</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>0.9999967323827974</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="4" t="n">
+        <v>203062.9214285714</v>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>796779.5941000001</v>
+      </c>
+      <c r="E77" s="4" t="n">
+        <v>178868.9821428572</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>10551.54761904762</v>
+      </c>
+      <c r="H77" s="4" t="n">
+        <v>1189263.045290476</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>1.000000004448533</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="4" t="n">
+        <v>416597.0481678573</v>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>659179.4523809523</v>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>288856.7345238095</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>44303.82050000001</v>
+      </c>
+      <c r="H78" s="4" t="n">
+        <v>1408937.055572619</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>1.008070422561875</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="4" t="n">
+        <v>189714.4888690476</v>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>345893.2417857143</v>
+      </c>
+      <c r="E79" s="4" t="n">
+        <v>36238.06666666667</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>6397.922619047619</v>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>578243.7199404762</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>1.000003868004183</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="n">
+        <v>562888.2817440477</v>
+      </c>
+      <c r="C80" s="4" t="n">
+        <v>232970.7238095239</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>562159.8574285716</v>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>122177.0345238095</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>3439.479761904762</v>
+      </c>
+      <c r="H80" s="4" t="n">
+        <v>1483635.377267857</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>0.9999886309394943</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="n">
+        <v>785008.531702381</v>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>161983.6628809524</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>203495.8786820833</v>
+      </c>
+      <c r="E81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v>2550.826190476191</v>
+      </c>
+      <c r="H81" s="4" t="n">
+        <v>1153038.899455893</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>0.9514789843718031</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I81"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W81"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="26" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="26" customWidth="1" min="22" max="22"/>
+    <col width="26" customWidth="1" min="23" max="23"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>mês</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Petroleo Brasileiro S A Petrobras</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Blueway Trading Importacao E Exportacao S.A.</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Oil Trading Importadora E Exportadora Ltda.</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Vibra Energia S.A</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Amazonia Energia Industria E Comercio De Combustiveis Ltda</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Refinaria De Manaus S.A.</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Wm Comercial Atacadista Ltda</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Nimofast Brasil S/A</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>Refinaria De Petroleos De Manguinhos S/A - Em Recuperacao Ju</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Sul Plata Trading Do Brasil Ltda</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Sertrading (Br) Ltda.</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Nfx Combustiveis Maritimos Ltda.</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Axa Oil Petroleo S.A</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Royal Fic Comercial Importadora E Exportadora Ltda</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Vibra Trading Importacao E Exportacao Ltda</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Royal Fic Distribuidora De Derivados De Petroleo Sa</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Greenergy Brasil Trading S.A.</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Wtb Trading Importacao E Exportacao Ltda</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Atem's Distribuidora De Petroleo S.A.</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Global Import Ltda</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>outras</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2020-01</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n">
+        <v>160368.7523809524</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>202468.3797619047</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>105856.4297619048</v>
+      </c>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n">
+        <v>71093.89285714287</v>
+      </c>
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n">
+        <v>133347.1809523809</v>
+      </c>
+      <c r="I2" s="4" t="n"/>
+      <c r="J2" s="4" t="n"/>
+      <c r="K2" s="4" t="n">
+        <v>55362.49642857142</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>86425.64404761905</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>34573.44880952381</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>9911.691666666668</v>
+      </c>
+      <c r="O2" s="4" t="n"/>
+      <c r="P2" s="4" t="n"/>
+      <c r="Q2" s="4" t="n"/>
+      <c r="R2" s="4" t="n">
+        <v>70968.3880952381</v>
+      </c>
+      <c r="S2" s="4" t="n"/>
+      <c r="T2" s="4" t="n"/>
+      <c r="U2" s="4" t="n">
+        <v>28548.90952380953</v>
+      </c>
+      <c r="V2" s="4" t="n">
+        <v>229140.2654761905</v>
+      </c>
+      <c r="W2" s="4" t="n">
+        <v>1188065.479761905</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2020-02</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>214189.8710714286</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>167619.0261904762</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>106001.6607142857</v>
+      </c>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n">
+        <v>98253.81071428572</v>
+      </c>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n">
+        <v>145417.4035714286</v>
+      </c>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n">
+        <v>34235.375</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>108409.2833333333</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>24759.37857142857</v>
+      </c>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n"/>
+      <c r="P3" s="4" t="n"/>
+      <c r="Q3" s="4" t="n"/>
+      <c r="R3" s="4" t="n">
+        <v>37576.21666666667</v>
+      </c>
+      <c r="S3" s="4" t="n"/>
+      <c r="T3" s="4" t="n"/>
+      <c r="U3" s="4" t="n">
+        <v>37684.59166666667</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>148738.6256190476</v>
+      </c>
+      <c r="W3" s="4" t="n">
+        <v>1122885.243119048</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2020-03</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n">
+        <v>234586.8821428572</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>96419.52976190476</v>
+      </c>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n">
+        <v>60953.73571428571</v>
+      </c>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n">
+        <v>118831.0547619048</v>
+      </c>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n">
+        <v>33352.09285714285</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>130978.5797619048</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>26719.40357142857</v>
+      </c>
+      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="4" t="n"/>
+      <c r="P4" s="4" t="n"/>
+      <c r="Q4" s="4" t="n"/>
+      <c r="R4" s="4" t="n">
+        <v>65597.17261904762</v>
+      </c>
+      <c r="S4" s="4" t="n"/>
+      <c r="T4" s="4" t="n"/>
+      <c r="U4" s="4" t="n">
+        <v>34484.2630952381</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>143894.6707238095</v>
+      </c>
+      <c r="W4" s="4" t="n">
+        <v>945817.3850095238</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2020-04</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n">
+        <v>205431.5583333333</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>151252.2892857143</v>
+      </c>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n">
+        <v>152069.3047619048</v>
+      </c>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="4" t="n">
+        <v>57429.90595238095</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>116619.7190476191</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>26637.06190476191</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>12081.75952380952</v>
+      </c>
+      <c r="O5" s="4" t="n"/>
+      <c r="P5" s="4" t="n"/>
+      <c r="Q5" s="4" t="n"/>
+      <c r="R5" s="4" t="n">
+        <v>52552.25952380952</v>
+      </c>
+      <c r="S5" s="4" t="n"/>
+      <c r="T5" s="4" t="n"/>
+      <c r="U5" s="4" t="n">
+        <v>47555.2</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>175517.2193334405</v>
+      </c>
+      <c r="W5" s="4" t="n">
+        <v>997146.2776667738</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2020-05</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n">
+        <v>263258.6380952381</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>106375.3357142857</v>
+      </c>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n">
+        <v>80097.68920833335</v>
+      </c>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n">
+        <v>9915.060714285715</v>
+      </c>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="4" t="n">
+        <v>26940.18333333333</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>21437.79166666666</v>
+      </c>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n">
+        <v>7911.50119047619</v>
+      </c>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="n"/>
+      <c r="Q6" s="4" t="n"/>
+      <c r="R6" s="4" t="n">
+        <v>21094.55714285714</v>
+      </c>
+      <c r="S6" s="4" t="n"/>
+      <c r="T6" s="4" t="n"/>
+      <c r="U6" s="4" t="n">
+        <v>23892.94642857143</v>
+      </c>
+      <c r="V6" s="4" t="n">
+        <v>144251.2228809524</v>
+      </c>
+      <c r="W6" s="4" t="n">
+        <v>705174.926375</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2020-06</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n">
+        <v>207310.194047619</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>145871.8214285714</v>
+      </c>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n">
+        <v>20802.39404761905</v>
+      </c>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n">
+        <v>203834.3</v>
+      </c>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="4" t="n">
+        <v>19669.51547619048</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>22403.7</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>1512.576190476191</v>
+      </c>
+      <c r="M7" s="4" t="n"/>
+      <c r="N7" s="4" t="n"/>
+      <c r="O7" s="4" t="n"/>
+      <c r="P7" s="4" t="n"/>
+      <c r="Q7" s="4" t="n"/>
+      <c r="R7" s="4" t="n">
+        <v>11838.50952380953</v>
+      </c>
+      <c r="S7" s="4" t="n"/>
+      <c r="T7" s="4" t="n"/>
+      <c r="U7" s="4" t="n">
+        <v>37048.2</v>
+      </c>
+      <c r="V7" s="4" t="n">
+        <v>164170.1301904762</v>
+      </c>
+      <c r="W7" s="4" t="n">
+        <v>834461.3409047618</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2020-07</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n">
+        <v>248707.4130952381</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>237069.0380952381</v>
+      </c>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="n">
+        <v>24765.02619047619</v>
+      </c>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="n">
+        <v>183125.4214285714</v>
+      </c>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="4" t="n">
+        <v>15823.07619047619</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>45951.95714285714</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>60525.14047619048</v>
+      </c>
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="4" t="n"/>
+      <c r="O8" s="4" t="n"/>
+      <c r="P8" s="4" t="n"/>
+      <c r="Q8" s="4" t="n"/>
+      <c r="R8" s="4" t="n">
+        <v>63612.34523809524</v>
+      </c>
+      <c r="S8" s="4" t="n"/>
+      <c r="T8" s="4" t="n"/>
+      <c r="U8" s="4" t="n">
+        <v>53733.80357142857</v>
+      </c>
+      <c r="V8" s="4" t="n">
+        <v>198202.8599047619</v>
+      </c>
+      <c r="W8" s="4" t="n">
+        <v>1131516.081333333</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2020-08</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>90785.34476190477</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>213602.5369047619</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>170908.0321428571</v>
+      </c>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="n">
+        <v>104281.9011904762</v>
+      </c>
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="n">
+        <v>167546.5904761905</v>
+      </c>
+      <c r="I9" s="4" t="n"/>
+      <c r="J9" s="4" t="n">
+        <v>7866.508333333334</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>12807.22142857143</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>101478.0130952381</v>
+      </c>
+      <c r="M9" s="4" t="n"/>
+      <c r="N9" s="4" t="n">
+        <v>26749.36666666667</v>
+      </c>
+      <c r="O9" s="4" t="n"/>
+      <c r="P9" s="4" t="n"/>
+      <c r="Q9" s="4" t="n"/>
+      <c r="R9" s="4" t="n">
+        <v>24615.91785714286</v>
+      </c>
+      <c r="S9" s="4" t="n"/>
+      <c r="T9" s="4" t="n"/>
+      <c r="U9" s="4" t="n">
+        <v>50663.54404761905</v>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>156621.1965608571</v>
+      </c>
+      <c r="W9" s="4" t="n">
+        <v>1127926.173465619</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2020-09</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>60587.72380952381</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>179042.6654761905</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>235405.7753571429</v>
+      </c>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n">
+        <v>34783.55952380953</v>
+      </c>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="n">
+        <v>95086.76666666668</v>
+      </c>
+      <c r="I10" s="4" t="n"/>
+      <c r="J10" s="4" t="n"/>
+      <c r="K10" s="4" t="n">
+        <v>34319.48095238095</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>78422.77380952382</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>16039.76904761905</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>18091.25595238095</v>
+      </c>
+      <c r="O10" s="4" t="n"/>
+      <c r="P10" s="4" t="n"/>
+      <c r="Q10" s="4" t="n"/>
+      <c r="R10" s="4" t="n">
+        <v>11325.27619047619</v>
+      </c>
+      <c r="S10" s="4" t="n"/>
+      <c r="T10" s="4" t="n"/>
+      <c r="U10" s="4" t="n">
+        <v>43565.61904761905</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>178691.3888558333</v>
+      </c>
+      <c r="W10" s="4" t="n">
+        <v>985362.0546891667</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2020-10</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>158156.3222619048</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>131214.0035714286</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>230842.5035714286</v>
+      </c>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n">
+        <v>27865.57023809524</v>
+      </c>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n">
+        <v>190704.055952381</v>
+      </c>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4" t="n">
+        <v>6930.169047619048</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>28152.06904761905</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>103028.3023809524</v>
+      </c>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n">
+        <v>6930.169047619048</v>
+      </c>
+      <c r="O11" s="4" t="n"/>
+      <c r="P11" s="4" t="n"/>
+      <c r="Q11" s="4" t="n"/>
+      <c r="R11" s="4" t="n">
+        <v>8897.888095238095</v>
+      </c>
+      <c r="S11" s="4" t="n"/>
+      <c r="T11" s="4" t="n"/>
+      <c r="U11" s="4" t="n">
+        <v>126732.0333333333</v>
+      </c>
+      <c r="V11" s="4" t="n">
+        <v>156523.1014285714</v>
+      </c>
+      <c r="W11" s="4" t="n">
+        <v>1175976.187976191</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2020-11</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n">
+        <v>166960.7047619048</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>185964.4880952381</v>
+      </c>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n">
+        <v>27049.30833333334</v>
+      </c>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n">
+        <v>106389.1619047619</v>
+      </c>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="4" t="n"/>
+      <c r="K12" s="4" t="n">
+        <v>17327.44642857143</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>117409.8726190476</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>16332.59880952381</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>23842.81785714286</v>
+      </c>
+      <c r="O12" s="4" t="n"/>
+      <c r="P12" s="4" t="n"/>
+      <c r="Q12" s="4" t="n"/>
+      <c r="R12" s="4" t="n">
+        <v>16762.50952380952</v>
+      </c>
+      <c r="S12" s="4" t="n"/>
+      <c r="T12" s="4" t="n"/>
+      <c r="U12" s="4" t="n">
+        <v>8036.757142857144</v>
+      </c>
+      <c r="V12" s="4" t="n">
+        <v>166045.2680238095</v>
+      </c>
+      <c r="W12" s="4" t="n">
+        <v>852120.9335</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2020-12</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>226367.8316666667</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>64016.07261904762</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>44354.70833333334</v>
+      </c>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n">
+        <v>9901.423809523811</v>
+      </c>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="n">
+        <v>167007.6738095238</v>
+      </c>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4" t="n"/>
+      <c r="K13" s="4" t="n">
+        <v>13547.10238095238</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>107285.8571428571</v>
+      </c>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n">
+        <v>23998.64523809524</v>
+      </c>
+      <c r="O13" s="4" t="n"/>
+      <c r="P13" s="4" t="n"/>
+      <c r="Q13" s="4" t="n"/>
+      <c r="R13" s="4" t="n">
+        <v>10948.87857142857</v>
+      </c>
+      <c r="S13" s="4" t="n"/>
+      <c r="T13" s="4" t="n"/>
+      <c r="U13" s="4" t="n"/>
+      <c r="V13" s="4" t="n">
+        <v>260675.6949428571</v>
+      </c>
+      <c r="W13" s="4" t="n">
+        <v>928103.8885142857</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2021-01</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>256480.7416666667</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>152379.6130952381</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>39701.74880952381</v>
+      </c>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n">
+        <v>58952.04761904763</v>
+      </c>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n">
+        <v>68918.87976190475</v>
+      </c>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="4" t="n"/>
+      <c r="K14" s="4" t="n">
+        <v>9753.844047619048</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>81514.10238095238</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>15641.74166666667</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>16419.74285714286</v>
+      </c>
+      <c r="O14" s="4" t="n"/>
+      <c r="P14" s="4" t="n"/>
+      <c r="Q14" s="4" t="n"/>
+      <c r="R14" s="4" t="n"/>
+      <c r="S14" s="4" t="n"/>
+      <c r="T14" s="4" t="n"/>
+      <c r="U14" s="4" t="n"/>
+      <c r="V14" s="4" t="n">
+        <v>91156.66428571429</v>
+      </c>
+      <c r="W14" s="4" t="n">
+        <v>790919.1261904762</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2021-02</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>178776.148452381</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>92456.10000000001</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>19080.40119047619</v>
+      </c>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n">
+        <v>53518.50357142857</v>
+      </c>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="n">
+        <v>127623.9369047619</v>
+      </c>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="4" t="n"/>
+      <c r="K15" s="4" t="n">
+        <v>12220.14285714286</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>141874.3095238095</v>
+      </c>
+      <c r="M15" s="4" t="n"/>
+      <c r="N15" s="4" t="n">
+        <v>17525.99285714286</v>
+      </c>
+      <c r="O15" s="4" t="n"/>
+      <c r="P15" s="4" t="n"/>
+      <c r="Q15" s="4" t="n"/>
+      <c r="R15" s="4" t="n">
+        <v>7635.386904761905</v>
+      </c>
+      <c r="S15" s="4" t="n"/>
+      <c r="T15" s="4" t="n"/>
+      <c r="U15" s="4" t="n"/>
+      <c r="V15" s="4" t="n">
+        <v>62128.03928571429</v>
+      </c>
+      <c r="W15" s="4" t="n">
+        <v>712838.9615476191</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2021-03</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>229285.2263095239</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>57485.64404761905</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>89709.73452380953</v>
+      </c>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n">
+        <v>25247.12380952381</v>
+      </c>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n">
+        <v>130824.0821428571</v>
+      </c>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="4" t="n"/>
+      <c r="K16" s="4" t="n">
+        <v>32147.51190476191</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>141309.4</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>15756.19880952381</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>41016.73452380953</v>
+      </c>
+      <c r="O16" s="4" t="n"/>
+      <c r="P16" s="4" t="n"/>
+      <c r="Q16" s="4" t="n"/>
+      <c r="R16" s="4" t="n">
+        <v>49126.96428571429</v>
+      </c>
+      <c r="S16" s="4" t="n"/>
+      <c r="T16" s="4" t="n"/>
+      <c r="U16" s="4" t="n">
+        <v>4924.039285714286</v>
+      </c>
+      <c r="V16" s="4" t="n">
+        <v>75470.61869047619</v>
+      </c>
+      <c r="W16" s="4" t="n">
+        <v>892303.2783333334</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2021-04</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>699163.0261904763</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>169827.5571428571</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>98639.66071428571</v>
+      </c>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n">
+        <v>39995.32023809524</v>
+      </c>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="n">
+        <v>130911.7083333333</v>
+      </c>
+      <c r="I17" s="4" t="n"/>
+      <c r="J17" s="4" t="n"/>
+      <c r="K17" s="4" t="n">
+        <v>50398.41904761905</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>48638.88452380953</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>6320.040476190476</v>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>43756.16428571429</v>
+      </c>
+      <c r="O17" s="4" t="n"/>
+      <c r="P17" s="4" t="n"/>
+      <c r="Q17" s="4" t="n"/>
+      <c r="R17" s="4" t="n">
+        <v>28896.07619047619</v>
+      </c>
+      <c r="S17" s="4" t="n"/>
+      <c r="T17" s="4" t="n"/>
+      <c r="U17" s="4" t="n">
+        <v>58844.20476190477</v>
+      </c>
+      <c r="V17" s="4" t="n">
+        <v>27053.35541654762</v>
+      </c>
+      <c r="W17" s="4" t="n">
+        <v>1402444.41732131</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2021-05</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>732102.1904761905</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>150917.6678571429</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>161235.6904761905</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>14803.8</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>110035.4285714286</v>
+      </c>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n">
+        <v>47850.34642857143</v>
+      </c>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="4" t="n">
+        <v>12400.0130952381</v>
+      </c>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n">
+        <v>10066.05476190476</v>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>67056.66428571429</v>
+      </c>
+      <c r="O18" s="4" t="n"/>
+      <c r="P18" s="4" t="n"/>
+      <c r="Q18" s="4" t="n"/>
+      <c r="R18" s="4" t="n"/>
+      <c r="S18" s="4" t="n"/>
+      <c r="T18" s="4" t="n"/>
+      <c r="U18" s="4" t="n">
+        <v>29240.91190476191</v>
+      </c>
+      <c r="V18" s="4" t="n">
+        <v>30054.22500000001</v>
+      </c>
+      <c r="W18" s="4" t="n">
+        <v>1365762.992857143</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>456028.4550000001</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>206045.2904761905</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>118379.4904761905</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>34160.84761904762</v>
+      </c>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n">
+        <v>133311.3464285714</v>
+      </c>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
+      <c r="K19" s="4" t="n">
+        <v>22371.23571428571</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>23424.96785714286</v>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>15691.8119047619</v>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>20514.96785714286</v>
+      </c>
+      <c r="O19" s="4" t="n"/>
+      <c r="P19" s="4" t="n"/>
+      <c r="Q19" s="4" t="n"/>
+      <c r="R19" s="4" t="n">
+        <v>22895.46785714286</v>
+      </c>
+      <c r="S19" s="4" t="n"/>
+      <c r="T19" s="4" t="n"/>
+      <c r="U19" s="4" t="n">
+        <v>27215.16071428571</v>
+      </c>
+      <c r="V19" s="4" t="n">
+        <v>52464.0430952381</v>
+      </c>
+      <c r="W19" s="4" t="n">
+        <v>1132503.085</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>465691.5839285714</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>176391.3452380952</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>90610.69523809524</v>
+      </c>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n">
+        <v>30108.625</v>
+      </c>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n">
+        <v>157466.1333333334</v>
+      </c>
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="4" t="n"/>
+      <c r="K20" s="4" t="n">
+        <v>45804.99880952381</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>100052.3595238095</v>
+      </c>
+      <c r="M20" s="4" t="n"/>
+      <c r="N20" s="4" t="n">
+        <v>15277.66428571429</v>
+      </c>
+      <c r="O20" s="4" t="n"/>
+      <c r="P20" s="4" t="n"/>
+      <c r="Q20" s="4" t="n"/>
+      <c r="R20" s="4" t="n">
+        <v>26647.60595238096</v>
+      </c>
+      <c r="S20" s="4" t="n"/>
+      <c r="T20" s="4" t="n"/>
+      <c r="U20" s="4" t="n">
+        <v>23860.88571428572</v>
+      </c>
+      <c r="V20" s="4" t="n">
+        <v>105346.0782143452</v>
+      </c>
+      <c r="W20" s="4" t="n">
+        <v>1237257.975238155</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>834286.1533333334</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>174792.0345238095</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>118730.5142857143</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>48945.43571428572</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>90229.91547619048</v>
+      </c>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n">
+        <v>151768.8261904762</v>
+      </c>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4" t="n"/>
+      <c r="K21" s="4" t="n">
+        <v>40959.45119047619</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>73964.66904761904</v>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>15886.22619047619</v>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>21144.46190476191</v>
+      </c>
+      <c r="O21" s="4" t="n"/>
+      <c r="P21" s="4" t="n"/>
+      <c r="Q21" s="4" t="n"/>
+      <c r="R21" s="4" t="n">
+        <v>33605.79761904762</v>
+      </c>
+      <c r="S21" s="4" t="n"/>
+      <c r="T21" s="4" t="n"/>
+      <c r="U21" s="4" t="n">
+        <v>9944.14642857143</v>
+      </c>
+      <c r="V21" s="4" t="n">
+        <v>58041.85</v>
+      </c>
+      <c r="W21" s="4" t="n">
+        <v>1672299.481904762</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2021-09</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>406162.4036904762</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>124725.5976190476</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>22414.62142857143</v>
+      </c>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n">
+        <v>58837.30357142857</v>
+      </c>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n">
+        <v>97008.7023809524</v>
+      </c>
+      <c r="I22" s="4" t="n"/>
+      <c r="J22" s="4" t="n"/>
+      <c r="K22" s="4" t="n">
+        <v>33700.10714285714</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>100205.9916666667</v>
+      </c>
+      <c r="M22" s="4" t="n">
+        <v>15966.35476190476</v>
+      </c>
+      <c r="N22" s="4" t="n">
+        <v>23372.69166666667</v>
+      </c>
+      <c r="O22" s="4" t="n"/>
+      <c r="P22" s="4" t="n"/>
+      <c r="Q22" s="4" t="n"/>
+      <c r="R22" s="4" t="n">
+        <v>12350.78571428572</v>
+      </c>
+      <c r="S22" s="4" t="n"/>
+      <c r="T22" s="4" t="n"/>
+      <c r="U22" s="4" t="n">
+        <v>34335.16904761905</v>
+      </c>
+      <c r="V22" s="4" t="n">
+        <v>45576.77619047619</v>
+      </c>
+      <c r="W22" s="4" t="n">
+        <v>974656.5048809524</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2021-10</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>1203351.686666667</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>109441.3380952381</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>91644.39523809525</v>
+      </c>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n">
+        <v>84458.88452380954</v>
+      </c>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="4" t="n">
+        <v>218929.3452380952</v>
+      </c>
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" s="4" t="n"/>
+      <c r="K23" s="4" t="n">
+        <v>20074.95119047619</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>12817.06785714286</v>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>15926.91821428572</v>
+      </c>
+      <c r="N23" s="4" t="n">
+        <v>57408.97142857143</v>
+      </c>
+      <c r="O23" s="4" t="n"/>
+      <c r="P23" s="4" t="n"/>
+      <c r="Q23" s="4" t="n"/>
+      <c r="R23" s="4" t="n">
+        <v>14852.98333333333</v>
+      </c>
+      <c r="S23" s="4" t="n"/>
+      <c r="T23" s="4" t="n"/>
+      <c r="U23" s="4" t="n">
+        <v>7427.479761904761</v>
+      </c>
+      <c r="V23" s="4" t="n">
+        <v>16744.02083333333</v>
+      </c>
+      <c r="W23" s="4" t="n">
+        <v>1853078.042380952</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>549028.1927380953</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>97411.52023809523</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>121099.2785714286</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>157267.9261904762</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>9836.863095238095</v>
+      </c>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n">
+        <v>59388.32500000001</v>
+      </c>
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="4" t="n"/>
+      <c r="K24" s="4" t="n">
+        <v>24701.93214285714</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>19758.45952380952</v>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>16203.36547619048</v>
+      </c>
+      <c r="N24" s="4" t="n">
+        <v>16778.87619047619</v>
+      </c>
+      <c r="O24" s="4" t="n"/>
+      <c r="P24" s="4" t="n"/>
+      <c r="Q24" s="4" t="n"/>
+      <c r="R24" s="4" t="n">
+        <v>21238.73571428571</v>
+      </c>
+      <c r="S24" s="4" t="n"/>
+      <c r="T24" s="4" t="n"/>
+      <c r="U24" s="4" t="n">
+        <v>24831.04285714286</v>
+      </c>
+      <c r="V24" s="4" t="n">
+        <v>17776.09482764286</v>
+      </c>
+      <c r="W24" s="4" t="n">
+        <v>1135320.612565738</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>342594.730952381</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>181174.3369047619</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>152785.8595238095</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>270455.9773809524</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>10062.23214285714</v>
+      </c>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="4" t="n">
+        <v>32971.78928571429</v>
+      </c>
+      <c r="I25" s="4" t="n"/>
+      <c r="J25" s="4" t="n"/>
+      <c r="K25" s="4" t="n">
+        <v>29305.00119047619</v>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>8589.907142857142</v>
+      </c>
+      <c r="M25" s="4" t="n">
+        <v>20011.79404761905</v>
+      </c>
+      <c r="N25" s="4" t="n">
+        <v>31003.94166666667</v>
+      </c>
+      <c r="O25" s="4" t="n"/>
+      <c r="P25" s="4" t="n"/>
+      <c r="Q25" s="4" t="n"/>
+      <c r="R25" s="4" t="n">
+        <v>19624.02023809524</v>
+      </c>
+      <c r="S25" s="4" t="n"/>
+      <c r="T25" s="4" t="n"/>
+      <c r="U25" s="4" t="n"/>
+      <c r="V25" s="4" t="n">
+        <v>51810.46739285714</v>
+      </c>
+      <c r="W25" s="4" t="n">
+        <v>1150390.057869048</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2022-01</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>474941.335</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>167908.3547619048</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>162972.5285714286</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>270141.9940476191</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>142029.0154761905</v>
+      </c>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n">
+        <v>19859.60833333333</v>
+      </c>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="4" t="n"/>
+      <c r="K26" s="4" t="n">
+        <v>9956.852380952381</v>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>17808.80595238095</v>
+      </c>
+      <c r="M26" s="4" t="n">
+        <v>20622.24761904762</v>
+      </c>
+      <c r="N26" s="4" t="n">
+        <v>22961.96666666667</v>
+      </c>
+      <c r="O26" s="4" t="n"/>
+      <c r="P26" s="4" t="n"/>
+      <c r="Q26" s="4" t="n"/>
+      <c r="R26" s="4" t="n">
+        <v>4416.428571428572</v>
+      </c>
+      <c r="S26" s="4" t="n"/>
+      <c r="T26" s="4" t="n"/>
+      <c r="U26" s="4" t="n"/>
+      <c r="V26" s="4" t="n">
+        <v>81479.52976190476</v>
+      </c>
+      <c r="W26" s="4" t="n">
+        <v>1395098.667142857</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2022-02</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>125071.8772619048</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>109445.1619047619</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>34343.24761904762</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>144034.2618928571</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>9978.852380952383</v>
+      </c>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n">
+        <v>49248.825</v>
+      </c>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="4" t="n"/>
+      <c r="K27" s="4" t="n"/>
+      <c r="L27" s="4" t="n"/>
+      <c r="M27" s="4" t="n">
+        <v>20816.92261904762</v>
+      </c>
+      <c r="N27" s="4" t="n">
+        <v>21100.225</v>
+      </c>
+      <c r="O27" s="4" t="n"/>
+      <c r="P27" s="4" t="n"/>
+      <c r="Q27" s="4" t="n"/>
+      <c r="R27" s="4" t="n"/>
+      <c r="S27" s="4" t="n"/>
+      <c r="T27" s="4" t="n"/>
+      <c r="U27" s="4" t="n"/>
+      <c r="V27" s="4" t="n">
+        <v>47995.59762103572</v>
+      </c>
+      <c r="W27" s="4" t="n">
+        <v>562034.9712996072</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2022-03</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>474604.3251190477</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>181413.4523809524</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>100549.8464285714</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>281132.7738095238</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>66562.64642857143</v>
+      </c>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n">
+        <v>9510.886904761906</v>
+      </c>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="n">
+        <v>24058.32142857143</v>
+      </c>
+      <c r="L28" s="4" t="n"/>
+      <c r="M28" s="4" t="n">
+        <v>13866.98928571429</v>
+      </c>
+      <c r="N28" s="4" t="n"/>
+      <c r="O28" s="4" t="n"/>
+      <c r="P28" s="4" t="n"/>
+      <c r="Q28" s="4" t="n"/>
+      <c r="R28" s="4" t="n"/>
+      <c r="S28" s="4" t="n"/>
+      <c r="T28" s="4" t="n"/>
+      <c r="U28" s="4" t="n"/>
+      <c r="V28" s="4" t="n">
+        <v>40634.24351190477</v>
+      </c>
+      <c r="W28" s="4" t="n">
+        <v>1192333.485297619</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>712839.0233333333</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>232863.8571428572</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>98925.45595238096</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>372362.1952380953</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>88460.95714285714</v>
+      </c>
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="4" t="n"/>
+      <c r="I29" s="4" t="n"/>
+      <c r="J29" s="4" t="n"/>
+      <c r="K29" s="4" t="n">
+        <v>14883.60238095238</v>
+      </c>
+      <c r="L29" s="4" t="n"/>
+      <c r="M29" s="4" t="n">
+        <v>25546.8955952381</v>
+      </c>
+      <c r="N29" s="4" t="n"/>
+      <c r="O29" s="4" t="n"/>
+      <c r="P29" s="4" t="n"/>
+      <c r="Q29" s="4" t="n"/>
+      <c r="R29" s="4" t="n"/>
+      <c r="S29" s="4" t="n"/>
+      <c r="T29" s="4" t="n"/>
+      <c r="U29" s="4" t="n"/>
+      <c r="V29" s="4" t="n">
+        <v>11706.58690476191</v>
+      </c>
+      <c r="W29" s="4" t="n">
+        <v>1557588.573690476</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2022-05</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>566619.5333333333</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>163016.6904761905</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>237595.8940476191</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>359067.5809523809</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>45789.45595238095</v>
+      </c>
+      <c r="G30" s="4" t="n"/>
+      <c r="H30" s="4" t="n"/>
+      <c r="I30" s="4" t="n"/>
+      <c r="J30" s="4" t="n"/>
+      <c r="K30" s="4" t="n">
+        <v>17273.10714285714</v>
+      </c>
+      <c r="L30" s="4" t="n"/>
+      <c r="M30" s="4" t="n"/>
+      <c r="N30" s="4" t="n"/>
+      <c r="O30" s="4" t="n"/>
+      <c r="P30" s="4" t="n"/>
+      <c r="Q30" s="4" t="n"/>
+      <c r="R30" s="4" t="n"/>
+      <c r="S30" s="4" t="n"/>
+      <c r="T30" s="4" t="n"/>
+      <c r="U30" s="4" t="n"/>
+      <c r="V30" s="4" t="n">
+        <v>58811.00745714286</v>
+      </c>
+      <c r="W30" s="4" t="n">
+        <v>1448173.269361905</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>306643.3928571428</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>65849.57023809524</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>112085.9904761905</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>322767.5805928571</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>94776.20476190477</v>
+      </c>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="n"/>
+      <c r="L31" s="4" t="n"/>
+      <c r="M31" s="4" t="n">
+        <v>19643.96428571429</v>
+      </c>
+      <c r="N31" s="4" t="n"/>
+      <c r="O31" s="4" t="n"/>
+      <c r="P31" s="4" t="n"/>
+      <c r="Q31" s="4" t="n"/>
+      <c r="R31" s="4" t="n"/>
+      <c r="S31" s="4" t="n"/>
+      <c r="T31" s="4" t="n"/>
+      <c r="U31" s="4" t="n"/>
+      <c r="V31" s="4" t="n">
+        <v>22029.16190476191</v>
+      </c>
+      <c r="W31" s="4" t="n">
+        <v>943795.8651166667</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2022-07</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>575861.3809523811</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>147012.8892857143</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>74863.17857142858</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>387876.9904761905</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>39703.54880952381</v>
+      </c>
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
+      <c r="K32" s="4" t="n">
+        <v>43074.40714285715</v>
+      </c>
+      <c r="L32" s="4" t="n"/>
+      <c r="M32" s="4" t="n">
+        <v>20963.11666666667</v>
+      </c>
+      <c r="N32" s="4" t="n"/>
+      <c r="O32" s="4" t="n"/>
+      <c r="P32" s="4" t="n"/>
+      <c r="Q32" s="4" t="n"/>
+      <c r="R32" s="4" t="n"/>
+      <c r="S32" s="4" t="n"/>
+      <c r="T32" s="4" t="n"/>
+      <c r="U32" s="4" t="n"/>
+      <c r="V32" s="4" t="n">
+        <v>47798.37055952381</v>
+      </c>
+      <c r="W32" s="4" t="n">
+        <v>1337153.882464286</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>953034.4201190476</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>181893.5464285714</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>145142.9666666667</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>365458.2440476191</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>45219.95833333334</v>
+      </c>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
+      <c r="K33" s="4" t="n">
+        <v>41592.59523809524</v>
+      </c>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="n">
+        <v>20573.18571428572</v>
+      </c>
+      <c r="N33" s="4" t="n"/>
+      <c r="O33" s="4" t="n"/>
+      <c r="P33" s="4" t="n"/>
+      <c r="Q33" s="4" t="n"/>
+      <c r="R33" s="4" t="n"/>
+      <c r="S33" s="4" t="n"/>
+      <c r="T33" s="4" t="n"/>
+      <c r="U33" s="4" t="n"/>
+      <c r="V33" s="4" t="n">
+        <v>93917.56309523809</v>
+      </c>
+      <c r="W33" s="4" t="n">
+        <v>1846832.479642857</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2022-09</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>1113585.639285714</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>213879.5321428571</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>132669.7547619048</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>322989.9595238095</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>64293.19047619047</v>
+      </c>
+      <c r="G34" s="4" t="n"/>
+      <c r="H34" s="4" t="n"/>
+      <c r="I34" s="4" t="n"/>
+      <c r="J34" s="4" t="n"/>
+      <c r="K34" s="4" t="n">
+        <v>24746.32261904762</v>
+      </c>
+      <c r="L34" s="4" t="n"/>
+      <c r="M34" s="4" t="n">
+        <v>21532.90952380952</v>
+      </c>
+      <c r="N34" s="4" t="n">
+        <v>40830.16785714286</v>
+      </c>
+      <c r="O34" s="4" t="n"/>
+      <c r="P34" s="4" t="n"/>
+      <c r="Q34" s="4" t="n">
+        <v>982.3642857142858</v>
+      </c>
+      <c r="R34" s="4" t="n"/>
+      <c r="S34" s="4" t="n"/>
+      <c r="T34" s="4" t="n"/>
+      <c r="U34" s="4" t="n"/>
+      <c r="V34" s="4" t="n">
+        <v>63287.94642874999</v>
+      </c>
+      <c r="W34" s="4" t="n">
+        <v>1998797.786904941</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>760279.9927690477</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>49885.23809523809</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>64688.57857142857</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>301330.9249999999</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>84664.39283333335</v>
+      </c>
+      <c r="G35" s="4" t="n"/>
+      <c r="H35" s="4" t="n"/>
+      <c r="I35" s="4" t="n"/>
+      <c r="J35" s="4" t="n"/>
+      <c r="K35" s="4" t="n">
+        <v>12202.16071428572</v>
+      </c>
+      <c r="L35" s="4" t="n"/>
+      <c r="M35" s="4" t="n">
+        <v>27286.39642857143</v>
+      </c>
+      <c r="N35" s="4" t="n">
+        <v>19067.07857142857</v>
+      </c>
+      <c r="O35" s="4" t="n"/>
+      <c r="P35" s="4" t="n"/>
+      <c r="Q35" s="4" t="n"/>
+      <c r="R35" s="4" t="n"/>
+      <c r="S35" s="4" t="n"/>
+      <c r="T35" s="4" t="n"/>
+      <c r="U35" s="4" t="n"/>
+      <c r="V35" s="4" t="n">
+        <v>139903.6142858929</v>
+      </c>
+      <c r="W35" s="4" t="n">
+        <v>1459308.377269226</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>150721.9130952381</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>30556.72738095238</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>51814.8630952381</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>243005.5142857143</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>52367.72261904762</v>
+      </c>
+      <c r="G36" s="4" t="n"/>
+      <c r="H36" s="4" t="n"/>
+      <c r="I36" s="4" t="n"/>
+      <c r="J36" s="4" t="n"/>
+      <c r="K36" s="4" t="n">
+        <v>2871.77261904762</v>
+      </c>
+      <c r="L36" s="4" t="n"/>
+      <c r="M36" s="4" t="n">
+        <v>22491.85357142858</v>
+      </c>
+      <c r="N36" s="4" t="n">
+        <v>34885.08690476191</v>
+      </c>
+      <c r="O36" s="4" t="n"/>
+      <c r="P36" s="4" t="n"/>
+      <c r="Q36" s="4" t="n">
+        <v>2008.564285714286</v>
+      </c>
+      <c r="R36" s="4" t="n"/>
+      <c r="S36" s="4" t="n"/>
+      <c r="T36" s="4" t="n"/>
+      <c r="U36" s="4" t="n"/>
+      <c r="V36" s="4" t="n">
+        <v>88646.42442857142</v>
+      </c>
+      <c r="W36" s="4" t="n">
+        <v>679370.4422857143</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2022-12</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>708122.8333333334</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>94944.11428571428</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>139662.2285714286</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>279443.0142857143</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>50091.47857142857</v>
+      </c>
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="n"/>
+      <c r="I37" s="4" t="n">
+        <v>35576.67023809524</v>
+      </c>
+      <c r="J37" s="4" t="n"/>
+      <c r="K37" s="4" t="n">
+        <v>25007.71071428571</v>
+      </c>
+      <c r="L37" s="4" t="n"/>
+      <c r="M37" s="4" t="n">
+        <v>19734.3880952381</v>
+      </c>
+      <c r="N37" s="4" t="n">
+        <v>35169.90238095239</v>
+      </c>
+      <c r="O37" s="4" t="n"/>
+      <c r="P37" s="4" t="n"/>
+      <c r="Q37" s="4" t="n"/>
+      <c r="R37" s="4" t="n"/>
+      <c r="S37" s="4" t="n"/>
+      <c r="T37" s="4" t="n"/>
+      <c r="U37" s="4" t="n">
+        <v>10301.47619047619</v>
+      </c>
+      <c r="V37" s="4" t="n">
+        <v>57575.74508470239</v>
+      </c>
+      <c r="W37" s="4" t="n">
+        <v>1455629.561751369</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>298002.2035714285</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>38250.59880952381</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>61288.69285714285</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>163450.8142857143</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>76064.20238095238</v>
+      </c>
+      <c r="G38" s="4" t="n"/>
+      <c r="H38" s="4" t="n"/>
+      <c r="I38" s="4" t="n"/>
+      <c r="J38" s="4" t="n"/>
+      <c r="K38" s="4" t="n">
+        <v>2440.938095238095</v>
+      </c>
+      <c r="L38" s="4" t="n"/>
+      <c r="M38" s="4" t="n"/>
+      <c r="N38" s="4" t="n">
+        <v>23421.9380952381</v>
+      </c>
+      <c r="O38" s="4" t="n"/>
+      <c r="P38" s="4" t="n"/>
+      <c r="Q38" s="4" t="n">
+        <v>998.0380952380953</v>
+      </c>
+      <c r="R38" s="4" t="n"/>
+      <c r="S38" s="4" t="n"/>
+      <c r="T38" s="4" t="n"/>
+      <c r="U38" s="4" t="n"/>
+      <c r="V38" s="4" t="n">
+        <v>77870.98214285714</v>
+      </c>
+      <c r="W38" s="4" t="n">
+        <v>741788.4083333333</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>483274.4595238095</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>20332.19404761905</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>78690.89642857143</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>139028.6488095238</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>70889.3130952381</v>
+      </c>
+      <c r="G39" s="4" t="n"/>
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="4" t="n">
+        <v>50303.94285714286</v>
+      </c>
+      <c r="J39" s="4" t="n"/>
+      <c r="K39" s="4" t="n">
+        <v>56608.00119047619</v>
+      </c>
+      <c r="L39" s="4" t="n"/>
+      <c r="M39" s="4" t="n">
+        <v>45079.85714285714</v>
+      </c>
+      <c r="N39" s="4" t="n">
+        <v>41544.40714285715</v>
+      </c>
+      <c r="O39" s="4" t="n"/>
+      <c r="P39" s="4" t="n"/>
+      <c r="Q39" s="4" t="n">
+        <v>2981.57619047619</v>
+      </c>
+      <c r="R39" s="4" t="n"/>
+      <c r="S39" s="4" t="n"/>
+      <c r="T39" s="4" t="n"/>
+      <c r="U39" s="4" t="n"/>
+      <c r="V39" s="4" t="n">
+        <v>41393.30952380953</v>
+      </c>
+      <c r="W39" s="4" t="n">
+        <v>1030126.605952381</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>643456.6047619048</v>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>149811.3892857143</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>106700.469047619</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>206666.8095238095</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>242543.3095238095</v>
+      </c>
+      <c r="G40" s="4" t="n"/>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="4" t="n">
+        <v>136232.7571428572</v>
+      </c>
+      <c r="J40" s="4" t="n"/>
+      <c r="K40" s="4" t="n">
+        <v>85052.89761904761</v>
+      </c>
+      <c r="L40" s="4" t="n"/>
+      <c r="M40" s="4" t="n">
+        <v>23627.31904761905</v>
+      </c>
+      <c r="N40" s="4" t="n">
+        <v>43965.31904761905</v>
+      </c>
+      <c r="O40" s="4" t="n"/>
+      <c r="P40" s="4" t="n"/>
+      <c r="Q40" s="4" t="n">
+        <v>14713.67023809524</v>
+      </c>
+      <c r="R40" s="4" t="n"/>
+      <c r="S40" s="4" t="n"/>
+      <c r="T40" s="4" t="n"/>
+      <c r="U40" s="4" t="n"/>
+      <c r="V40" s="4" t="n">
+        <v>65636.19426190476</v>
+      </c>
+      <c r="W40" s="4" t="n">
+        <v>1718406.7395</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>116297.8690476191</v>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>25948.14047619048</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>111018.4392857143</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>127151.2035714286</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>76768.82261904763</v>
+      </c>
+      <c r="G41" s="4" t="n"/>
+      <c r="H41" s="4" t="n"/>
+      <c r="I41" s="4" t="n">
+        <v>150589.7678571428</v>
+      </c>
+      <c r="J41" s="4" t="n"/>
+      <c r="K41" s="4" t="n">
+        <v>82421.70714285714</v>
+      </c>
+      <c r="L41" s="4" t="n"/>
+      <c r="M41" s="4" t="n">
+        <v>24408.58690476191</v>
+      </c>
+      <c r="N41" s="4" t="n">
+        <v>79337.79880952381</v>
+      </c>
+      <c r="O41" s="4" t="n"/>
+      <c r="P41" s="4" t="n"/>
+      <c r="Q41" s="4" t="n">
+        <v>15774.28452380952</v>
+      </c>
+      <c r="R41" s="4" t="n"/>
+      <c r="S41" s="4" t="n"/>
+      <c r="T41" s="4" t="n"/>
+      <c r="U41" s="4" t="n"/>
+      <c r="V41" s="4" t="n">
+        <v>122678.230952381</v>
+      </c>
+      <c r="W41" s="4" t="n">
+        <v>932394.8511904762</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>499050.8892857143</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>6831.410714285715</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>144523.5464285715</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>84296.91190476192</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>109042.1892857143</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>111793.1666666667</v>
+      </c>
+      <c r="H42" s="4" t="n"/>
+      <c r="I42" s="4" t="n">
+        <v>133120.8178571429</v>
+      </c>
+      <c r="J42" s="4" t="n"/>
+      <c r="K42" s="4" t="n">
+        <v>48204.42023809524</v>
+      </c>
+      <c r="L42" s="4" t="n"/>
+      <c r="M42" s="4" t="n"/>
+      <c r="N42" s="4" t="n">
+        <v>47485.02619047619</v>
+      </c>
+      <c r="O42" s="4" t="n"/>
+      <c r="P42" s="4" t="n"/>
+      <c r="Q42" s="4" t="n">
+        <v>34687.5</v>
+      </c>
+      <c r="R42" s="4" t="n"/>
+      <c r="S42" s="4" t="n"/>
+      <c r="T42" s="4" t="n"/>
+      <c r="U42" s="4" t="n"/>
+      <c r="V42" s="4" t="n">
+        <v>144076.8833333333</v>
+      </c>
+      <c r="W42" s="4" t="n">
+        <v>1363112.761904762</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>230819.8583333333</v>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>48765.5738095238</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>97497.72499999999</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>94279.72500000001</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>75474.42857142857</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>92763.17261904762</v>
+      </c>
+      <c r="H43" s="4" t="n"/>
+      <c r="I43" s="4" t="n">
+        <v>118890.2273809524</v>
+      </c>
+      <c r="J43" s="4" t="n"/>
+      <c r="K43" s="4" t="n">
+        <v>43991.41190476191</v>
+      </c>
+      <c r="L43" s="4" t="n"/>
+      <c r="M43" s="4" t="n">
+        <v>20865.62142857143</v>
+      </c>
+      <c r="N43" s="4" t="n">
+        <v>117574.9273809524</v>
+      </c>
+      <c r="O43" s="4" t="n"/>
+      <c r="P43" s="4" t="n"/>
+      <c r="Q43" s="4" t="n">
+        <v>39915.52380952382</v>
+      </c>
+      <c r="R43" s="4" t="n"/>
+      <c r="S43" s="4" t="n"/>
+      <c r="T43" s="4" t="n"/>
+      <c r="U43" s="4" t="n"/>
+      <c r="V43" s="4" t="n">
+        <v>99202.1619047619</v>
+      </c>
+      <c r="W43" s="4" t="n">
+        <v>1080040.357142857</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>470739.6566666667</v>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>73120.72619047618</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>113428.6230952381</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>107969.455952381</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>9837.890476190476</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>29320.44404761905</v>
+      </c>
+      <c r="H44" s="4" t="n"/>
+      <c r="I44" s="4" t="n">
+        <v>55414.83333333334</v>
+      </c>
+      <c r="J44" s="4" t="n"/>
+      <c r="K44" s="4" t="n">
+        <v>27637.07023809524</v>
+      </c>
+      <c r="L44" s="4" t="n"/>
+      <c r="M44" s="4" t="n">
+        <v>21073.4880952381</v>
+      </c>
+      <c r="N44" s="4" t="n">
+        <v>47128.85595238095</v>
+      </c>
+      <c r="O44" s="4" t="n"/>
+      <c r="P44" s="4" t="n"/>
+      <c r="Q44" s="4" t="n">
+        <v>12767.84404761905</v>
+      </c>
+      <c r="R44" s="4" t="n"/>
+      <c r="S44" s="4" t="n"/>
+      <c r="T44" s="4" t="n"/>
+      <c r="U44" s="4" t="n"/>
+      <c r="V44" s="4" t="n">
+        <v>100390.5416428571</v>
+      </c>
+      <c r="W44" s="4" t="n">
+        <v>1068829.429738095</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>240317.9847738096</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>158624.3690476191</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>191945.430952381</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>12146.5</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>76345.06428571428</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>86413.41904761904</v>
+      </c>
+      <c r="H45" s="4" t="n"/>
+      <c r="I45" s="4" t="n">
+        <v>244652.0345238095</v>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>39170.80476190476</v>
+      </c>
+      <c r="K45" s="4" t="n">
+        <v>72185.62380952381</v>
+      </c>
+      <c r="L45" s="4" t="n"/>
+      <c r="M45" s="4" t="n">
+        <v>20491.26904761905</v>
+      </c>
+      <c r="N45" s="4" t="n">
+        <v>39164.90833333333</v>
+      </c>
+      <c r="O45" s="4" t="n"/>
+      <c r="P45" s="4" t="n"/>
+      <c r="Q45" s="4" t="n">
+        <v>28410.94761904762</v>
+      </c>
+      <c r="R45" s="4" t="n"/>
+      <c r="S45" s="4" t="n"/>
+      <c r="T45" s="4" t="n"/>
+      <c r="U45" s="4" t="n"/>
+      <c r="V45" s="4" t="n">
+        <v>98360.58690476192</v>
+      </c>
+      <c r="W45" s="4" t="n">
+        <v>1308228.943107143</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="n">
+        <v>274184.6963095238</v>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>93644.29166666667</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>149681.6642857143</v>
+      </c>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n">
+        <v>75599.75083333332</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>71806.91785714286</v>
+      </c>
+      <c r="H46" s="4" t="n"/>
+      <c r="I46" s="4" t="n">
+        <v>119868.0880952381</v>
+      </c>
+      <c r="J46" s="4" t="n"/>
+      <c r="K46" s="4" t="n">
+        <v>39577.61904761905</v>
+      </c>
+      <c r="L46" s="4" t="n"/>
+      <c r="M46" s="4" t="n">
+        <v>22593.92738095238</v>
+      </c>
+      <c r="N46" s="4" t="n">
+        <v>74755.6011904762</v>
+      </c>
+      <c r="O46" s="4" t="n"/>
+      <c r="P46" s="4" t="n"/>
+      <c r="Q46" s="4" t="n">
+        <v>3444.178571428572</v>
+      </c>
+      <c r="R46" s="4" t="n"/>
+      <c r="S46" s="4" t="n"/>
+      <c r="T46" s="4" t="n"/>
+      <c r="U46" s="4" t="n"/>
+      <c r="V46" s="4" t="n">
+        <v>210172.8620833334</v>
+      </c>
+      <c r="W46" s="4" t="n">
+        <v>1135329.597321429</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="n">
+        <v>248903.1702380952</v>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>496067.6933345238</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>193443.5666666667</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>130673.3273809524</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>14288.98214285714</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>37006.21547619047</v>
+      </c>
+      <c r="H47" s="4" t="n"/>
+      <c r="I47" s="4" t="n">
+        <v>159693.2666666667</v>
+      </c>
+      <c r="J47" s="4" t="n"/>
+      <c r="K47" s="4" t="n">
+        <v>57299.50000000001</v>
+      </c>
+      <c r="L47" s="4" t="n"/>
+      <c r="M47" s="4" t="n">
+        <v>23462.81785714286</v>
+      </c>
+      <c r="N47" s="4" t="n">
+        <v>71190.14047619049</v>
+      </c>
+      <c r="O47" s="4" t="n"/>
+      <c r="P47" s="4" t="n"/>
+      <c r="Q47" s="4" t="n">
+        <v>21999.67738095238</v>
+      </c>
+      <c r="R47" s="4" t="n"/>
+      <c r="S47" s="4" t="n"/>
+      <c r="T47" s="4" t="n"/>
+      <c r="U47" s="4" t="n"/>
+      <c r="V47" s="4" t="n">
+        <v>37325.625</v>
+      </c>
+      <c r="W47" s="4" t="n">
+        <v>1491353.982620238</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>271309.7666666667</v>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>129989.1392857143</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>146334.3892857143</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>39406.46785714286</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>56338.39285714286</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>32496.77976190476</v>
+      </c>
+      <c r="H48" s="4" t="n"/>
+      <c r="I48" s="4" t="n">
+        <v>73606.95714285714</v>
+      </c>
+      <c r="J48" s="4" t="n">
+        <v>5911.295238095238</v>
+      </c>
+      <c r="K48" s="4" t="n">
+        <v>20317.24642857143</v>
+      </c>
+      <c r="L48" s="4" t="n"/>
+      <c r="M48" s="4" t="n">
+        <v>21474.74642857143</v>
+      </c>
+      <c r="N48" s="4" t="n">
+        <v>72415.72380952381</v>
+      </c>
+      <c r="O48" s="4" t="n"/>
+      <c r="P48" s="4" t="n"/>
+      <c r="Q48" s="4" t="n">
+        <v>58418.72023809524</v>
+      </c>
+      <c r="R48" s="4" t="n"/>
+      <c r="S48" s="4" t="n"/>
+      <c r="T48" s="4" t="n"/>
+      <c r="U48" s="4" t="n"/>
+      <c r="V48" s="4" t="n">
+        <v>97915.78405339285</v>
+      </c>
+      <c r="W48" s="4" t="n">
+        <v>1025935.409053393</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>131636.7976190476</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>499479.3714285715</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>266881.3011904762</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>67945.12619047619</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>100783.0773809524</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>78980.14404761905</v>
+      </c>
+      <c r="H49" s="4" t="n"/>
+      <c r="I49" s="4" t="n">
+        <v>162709.6190476191</v>
+      </c>
+      <c r="J49" s="4" t="n">
+        <v>78744.83452380952</v>
+      </c>
+      <c r="K49" s="4" t="n">
+        <v>39533.83690476191</v>
+      </c>
+      <c r="L49" s="4" t="n"/>
+      <c r="M49" s="4" t="n">
+        <v>26742.24880952381</v>
+      </c>
+      <c r="N49" s="4" t="n"/>
+      <c r="O49" s="4" t="n"/>
+      <c r="P49" s="4" t="n"/>
+      <c r="Q49" s="4" t="n">
+        <v>92767.32261904761</v>
+      </c>
+      <c r="R49" s="4" t="n"/>
+      <c r="S49" s="4" t="n"/>
+      <c r="T49" s="4" t="n"/>
+      <c r="U49" s="4" t="n"/>
+      <c r="V49" s="4" t="n">
+        <v>331984.3147155476</v>
+      </c>
+      <c r="W49" s="4" t="n">
+        <v>1878187.994477452</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>189232.4571428572</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>5945.164285714285</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>109894.4595238095</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>125538.4714285714</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>102968.7583333333</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>65788.40119047619</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>8880.835714285715</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>127994.3011904762</v>
+      </c>
+      <c r="J50" s="4" t="n">
+        <v>39157.48928571428</v>
+      </c>
+      <c r="K50" s="4" t="n">
+        <v>44343.79285714286</v>
+      </c>
+      <c r="L50" s="4" t="n"/>
+      <c r="M50" s="4" t="n">
+        <v>20936.33095238095</v>
+      </c>
+      <c r="N50" s="4" t="n"/>
+      <c r="O50" s="4" t="n"/>
+      <c r="P50" s="4" t="n"/>
+      <c r="Q50" s="4" t="n">
+        <v>37524.425</v>
+      </c>
+      <c r="R50" s="4" t="n"/>
+      <c r="S50" s="4" t="n"/>
+      <c r="T50" s="4" t="n"/>
+      <c r="U50" s="4" t="n"/>
+      <c r="V50" s="4" t="n">
+        <v>168591.4565714286</v>
+      </c>
+      <c r="W50" s="4" t="n">
+        <v>1046796.34347619</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>243694.1404761905</v>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>9853.347619047619</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>70450.22857142857</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>89931.88571428572</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>77936.96190476191</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>78365.50595238095</v>
+      </c>
+      <c r="H51" s="4" t="n"/>
+      <c r="I51" s="4" t="n">
+        <v>9837.795238095237</v>
+      </c>
+      <c r="J51" s="4" t="n">
+        <v>44640.93928571429</v>
+      </c>
+      <c r="K51" s="4" t="n"/>
+      <c r="L51" s="4" t="n"/>
+      <c r="M51" s="4" t="n">
+        <v>21204.16547619048</v>
+      </c>
+      <c r="N51" s="4" t="n"/>
+      <c r="O51" s="4" t="n">
+        <v>4465.321428571428</v>
+      </c>
+      <c r="P51" s="4" t="n"/>
+      <c r="Q51" s="4" t="n">
+        <v>4960.555952380952</v>
+      </c>
+      <c r="R51" s="4" t="n"/>
+      <c r="S51" s="4" t="n"/>
+      <c r="T51" s="4" t="n"/>
+      <c r="U51" s="4" t="n"/>
+      <c r="V51" s="4" t="n">
+        <v>201885.6047619048</v>
+      </c>
+      <c r="W51" s="4" t="n">
+        <v>857226.4523809524</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>475145.7785714286</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>64248.16666666667</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>29423.3380952381</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>103426.469047619</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>90827.77499999999</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>116131.3964285714</v>
+      </c>
+      <c r="H52" s="4" t="n"/>
+      <c r="I52" s="4" t="n">
+        <v>23650.50119047619</v>
+      </c>
+      <c r="J52" s="4" t="n">
+        <v>79713.80357142858</v>
+      </c>
+      <c r="K52" s="4" t="n">
+        <v>25123.31547619048</v>
+      </c>
+      <c r="L52" s="4" t="n"/>
+      <c r="M52" s="4" t="n">
+        <v>21938.29285714286</v>
+      </c>
+      <c r="N52" s="4" t="n"/>
+      <c r="O52" s="4" t="n">
+        <v>25757.11547619048</v>
+      </c>
+      <c r="P52" s="4" t="n"/>
+      <c r="Q52" s="4" t="n">
+        <v>9884.666666666668</v>
+      </c>
+      <c r="R52" s="4" t="n"/>
+      <c r="S52" s="4" t="n"/>
+      <c r="T52" s="4" t="n"/>
+      <c r="U52" s="4" t="n"/>
+      <c r="V52" s="4" t="n">
+        <v>173844.7016897857</v>
+      </c>
+      <c r="W52" s="4" t="n">
+        <v>1239115.320737405</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n">
+        <v>353917.455952381</v>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>175986.2357142857</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>61339.91785714286</v>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>89800.96428571429</v>
+      </c>
+      <c r="F53" s="4" t="n"/>
+      <c r="G53" s="4" t="n">
+        <v>50322.52857142857</v>
+      </c>
+      <c r="H53" s="4" t="n"/>
+      <c r="I53" s="4" t="n">
+        <v>54466.34523809524</v>
+      </c>
+      <c r="J53" s="4" t="n">
+        <v>91015.82500000001</v>
+      </c>
+      <c r="K53" s="4" t="n">
+        <v>29825.14642857143</v>
+      </c>
+      <c r="L53" s="4" t="n"/>
+      <c r="M53" s="4" t="n">
+        <v>21564.47619047619</v>
+      </c>
+      <c r="N53" s="4" t="n"/>
+      <c r="O53" s="4" t="n">
+        <v>7904.491666666667</v>
+      </c>
+      <c r="P53" s="4" t="n">
+        <v>981.4309523809525</v>
+      </c>
+      <c r="Q53" s="4" t="n">
+        <v>23870.82023809524</v>
+      </c>
+      <c r="R53" s="4" t="n"/>
+      <c r="S53" s="4" t="n"/>
+      <c r="T53" s="4" t="n">
+        <v>49997.9</v>
+      </c>
+      <c r="U53" s="4" t="n"/>
+      <c r="V53" s="4" t="n">
+        <v>159774.3083333333</v>
+      </c>
+      <c r="W53" s="4" t="n">
+        <v>1170767.846428572</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="n"/>
+      <c r="C54" s="4" t="n">
+        <v>229981.3714285714</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>175814.3214285714</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>118016.9547619048</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>29547.18452380952</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>35194.13571428572</v>
+      </c>
+      <c r="H54" s="4" t="n"/>
+      <c r="I54" s="4" t="n">
+        <v>197415.4261904762</v>
+      </c>
+      <c r="J54" s="4" t="n">
+        <v>78340.76190476191</v>
+      </c>
+      <c r="K54" s="4" t="n">
+        <v>9831.947619047618</v>
+      </c>
+      <c r="L54" s="4" t="n"/>
+      <c r="M54" s="4" t="n">
+        <v>21475.94761904762</v>
+      </c>
+      <c r="N54" s="4" t="n"/>
+      <c r="O54" s="4" t="n">
+        <v>41033.26309523809</v>
+      </c>
+      <c r="P54" s="4" t="n">
+        <v>495.4142857142858</v>
+      </c>
+      <c r="Q54" s="4" t="n">
+        <v>60810.92976190476</v>
+      </c>
+      <c r="R54" s="4" t="n"/>
+      <c r="S54" s="4" t="n"/>
+      <c r="T54" s="4" t="n">
+        <v>36674.31904761905</v>
+      </c>
+      <c r="U54" s="4" t="n"/>
+      <c r="V54" s="4" t="n">
+        <v>34341.26071428572</v>
+      </c>
+      <c r="W54" s="4" t="n">
+        <v>1068973.238095238</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="n">
+        <v>409174.4238095239</v>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>278827.7452380952</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>65839.02857142857</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>217177.5226190476</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>22332.89761904762</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>24732.4880952381</v>
+      </c>
+      <c r="H55" s="4" t="n"/>
+      <c r="I55" s="4" t="n">
+        <v>76207.51071428572</v>
+      </c>
+      <c r="J55" s="4" t="n">
+        <v>39164.44047619047</v>
+      </c>
+      <c r="K55" s="4" t="n">
+        <v>14765.50714285714</v>
+      </c>
+      <c r="L55" s="4" t="n"/>
+      <c r="M55" s="4" t="n">
+        <v>21666.25119047619</v>
+      </c>
+      <c r="N55" s="4" t="n"/>
+      <c r="O55" s="4" t="n">
+        <v>61112.64285714286</v>
+      </c>
+      <c r="P55" s="4" t="n">
+        <v>3944.667857142857</v>
+      </c>
+      <c r="Q55" s="4" t="n">
+        <v>24948.20476190476</v>
+      </c>
+      <c r="R55" s="4" t="n"/>
+      <c r="S55" s="4" t="n"/>
+      <c r="T55" s="4" t="n">
+        <v>96719.77738095238</v>
+      </c>
+      <c r="U55" s="4" t="n"/>
+      <c r="V55" s="4" t="n">
+        <v>157610.7499168571</v>
+      </c>
+      <c r="W55" s="4" t="n">
+        <v>1514223.858250191</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="n">
+        <v>267992.0480952381</v>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>212034.825</v>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>93168.11547619049</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>164498.1773809524</v>
+      </c>
+      <c r="F56" s="4" t="n"/>
+      <c r="G56" s="4" t="n">
+        <v>91568.99880952382</v>
+      </c>
+      <c r="H56" s="4" t="n"/>
+      <c r="I56" s="4" t="n">
+        <v>60253.1619047619</v>
+      </c>
+      <c r="J56" s="4" t="n">
+        <v>132400.5738095238</v>
+      </c>
+      <c r="K56" s="4" t="n">
+        <v>11299.10833333333</v>
+      </c>
+      <c r="L56" s="4" t="n"/>
+      <c r="M56" s="4" t="n">
+        <v>25706.19642857143</v>
+      </c>
+      <c r="N56" s="4" t="n"/>
+      <c r="O56" s="4" t="n">
+        <v>34847.90952380953</v>
+      </c>
+      <c r="P56" s="4" t="n"/>
+      <c r="Q56" s="4" t="n">
+        <v>38149.07976190477</v>
+      </c>
+      <c r="R56" s="4" t="n"/>
+      <c r="S56" s="4" t="n"/>
+      <c r="T56" s="4" t="n">
+        <v>29994.88690476191</v>
+      </c>
+      <c r="U56" s="4" t="n"/>
+      <c r="V56" s="4" t="n">
+        <v>86102.26733333334</v>
+      </c>
+      <c r="W56" s="4" t="n">
+        <v>1248015.348761905</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="n">
+        <v>363857.5083333334</v>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>162175.6857142857</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>96015.87857142859</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>145280.4154761905</v>
+      </c>
+      <c r="F57" s="4" t="n"/>
+      <c r="G57" s="4" t="n">
+        <v>160796.7464285714</v>
+      </c>
+      <c r="H57" s="4" t="n"/>
+      <c r="I57" s="4" t="n">
+        <v>75034.50238095238</v>
+      </c>
+      <c r="J57" s="4" t="n">
+        <v>123588.8880952381</v>
+      </c>
+      <c r="K57" s="4" t="n"/>
+      <c r="L57" s="4" t="n"/>
+      <c r="M57" s="4" t="n">
+        <v>35037.05238095238</v>
+      </c>
+      <c r="N57" s="4" t="n"/>
+      <c r="O57" s="4" t="n">
+        <v>19018.95714285714</v>
+      </c>
+      <c r="P57" s="4" t="n"/>
+      <c r="Q57" s="4" t="n">
+        <v>9819.905952380952</v>
+      </c>
+      <c r="R57" s="4" t="n"/>
+      <c r="S57" s="4" t="n"/>
+      <c r="T57" s="4" t="n">
+        <v>2954.577380952381</v>
+      </c>
+      <c r="U57" s="4" t="n"/>
+      <c r="V57" s="4" t="n">
+        <v>72617.47619047618</v>
+      </c>
+      <c r="W57" s="4" t="n">
+        <v>1266197.594047619</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="n">
+        <v>432480.9369047619</v>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>262527.4964285715</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>223692.6345238095</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>152964.9607142857</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>70959.97857142857</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>84784.51904761905</v>
+      </c>
+      <c r="H58" s="4" t="n"/>
+      <c r="I58" s="4" t="n">
+        <v>50399.50952380953</v>
+      </c>
+      <c r="J58" s="4" t="n">
+        <v>132777.75</v>
+      </c>
+      <c r="K58" s="4" t="n"/>
+      <c r="L58" s="4" t="n"/>
+      <c r="M58" s="4" t="n">
+        <v>21980.51071428572</v>
+      </c>
+      <c r="N58" s="4" t="n"/>
+      <c r="O58" s="4" t="n">
+        <v>21652.5130952381</v>
+      </c>
+      <c r="P58" s="4" t="n"/>
+      <c r="Q58" s="4" t="n"/>
+      <c r="R58" s="4" t="n"/>
+      <c r="S58" s="4" t="n"/>
+      <c r="T58" s="4" t="n">
+        <v>18780.31071428572</v>
+      </c>
+      <c r="U58" s="4" t="n"/>
+      <c r="V58" s="4" t="n">
+        <v>122687.6007142857</v>
+      </c>
+      <c r="W58" s="4" t="n">
+        <v>1595688.720952381</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="n">
+        <v>239263.0036666667</v>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>294371.2404761905</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>112216.9607142857</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>270626.4345238095</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>8438.842857142858</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>180295.8476190476</v>
+      </c>
+      <c r="H59" s="4" t="n"/>
+      <c r="I59" s="4" t="n">
+        <v>34948.5130952381</v>
+      </c>
+      <c r="J59" s="4" t="n">
+        <v>132528.6869047619</v>
+      </c>
+      <c r="K59" s="4" t="n">
+        <v>47071.06904761904</v>
+      </c>
+      <c r="L59" s="4" t="n"/>
+      <c r="M59" s="4" t="n"/>
+      <c r="N59" s="4" t="n"/>
+      <c r="O59" s="4" t="n">
+        <v>32723.39166666667</v>
+      </c>
+      <c r="P59" s="4" t="n"/>
+      <c r="Q59" s="4" t="n">
+        <v>26432.66309523809</v>
+      </c>
+      <c r="R59" s="4" t="n"/>
+      <c r="S59" s="4" t="n"/>
+      <c r="T59" s="4" t="n"/>
+      <c r="U59" s="4" t="n"/>
+      <c r="V59" s="4" t="n">
+        <v>110546.4611073214</v>
+      </c>
+      <c r="W59" s="4" t="n">
+        <v>1489463.114773988</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="n"/>
+      <c r="C60" s="4" t="n">
+        <v>109257.2535714286</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>125906.1357261905</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>150859.8535714286</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>8881.772619047621</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>66143.09642857143</v>
+      </c>
+      <c r="H60" s="4" t="n"/>
+      <c r="I60" s="4" t="n">
+        <v>8303.742857142857</v>
+      </c>
+      <c r="J60" s="4" t="n">
+        <v>83079.94166666667</v>
+      </c>
+      <c r="K60" s="4" t="n">
+        <v>5884.394047619047</v>
+      </c>
+      <c r="L60" s="4" t="n"/>
+      <c r="M60" s="4" t="n">
+        <v>45935.6761904762</v>
+      </c>
+      <c r="N60" s="4" t="n"/>
+      <c r="O60" s="4" t="n">
+        <v>21449.35357142857</v>
+      </c>
+      <c r="P60" s="4" t="n"/>
+      <c r="Q60" s="4" t="n">
+        <v>27716.12261904762</v>
+      </c>
+      <c r="R60" s="4" t="n"/>
+      <c r="S60" s="4" t="n"/>
+      <c r="T60" s="4" t="n"/>
+      <c r="U60" s="4" t="n"/>
+      <c r="V60" s="4" t="n">
+        <v>181029.1651427738</v>
+      </c>
+      <c r="W60" s="4" t="n">
+        <v>834446.5080118215</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="n">
+        <v>243329.3203333333</v>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>105151.3511904762</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>53149.60952380953</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>49246.68690476191</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>19744.73690476191</v>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>92810.93571428573</v>
+      </c>
+      <c r="H61" s="4" t="n"/>
+      <c r="I61" s="4" t="n">
+        <v>8094.215476190477</v>
+      </c>
+      <c r="J61" s="4" t="n">
+        <v>145389.9738095238</v>
+      </c>
+      <c r="K61" s="4" t="n">
+        <v>20639.825</v>
+      </c>
+      <c r="L61" s="4" t="n"/>
+      <c r="M61" s="4" t="n">
+        <v>23901.225</v>
+      </c>
+      <c r="N61" s="4" t="n"/>
+      <c r="O61" s="4" t="n">
+        <v>23608.95714285714</v>
+      </c>
+      <c r="P61" s="4" t="n">
+        <v>3927.49880952381</v>
+      </c>
+      <c r="Q61" s="4" t="n">
+        <v>16183.44166666667</v>
+      </c>
+      <c r="R61" s="4" t="n"/>
+      <c r="S61" s="4" t="n"/>
+      <c r="T61" s="4" t="n">
+        <v>44791.35595238095</v>
+      </c>
+      <c r="U61" s="4" t="n"/>
+      <c r="V61" s="4" t="n">
+        <v>125086.662187619</v>
+      </c>
+      <c r="W61" s="4" t="n">
+        <v>975055.7956161905</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="n">
+        <v>371363.1952380952</v>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>97439.23333333334</v>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>49821.73928571428</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>89597.91071428571</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>65022.14166666668</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>115043.7285714286</v>
+      </c>
+      <c r="H62" s="4" t="n"/>
+      <c r="I62" s="4" t="n">
+        <v>26588.22023809524</v>
+      </c>
+      <c r="J62" s="4" t="n">
+        <v>129372.2071428571</v>
+      </c>
+      <c r="K62" s="4" t="n"/>
+      <c r="L62" s="4" t="n"/>
+      <c r="M62" s="4" t="n">
+        <v>22910.07976190476</v>
+      </c>
+      <c r="N62" s="4" t="n"/>
+      <c r="O62" s="4" t="n">
+        <v>70118.36666666667</v>
+      </c>
+      <c r="P62" s="4" t="n">
+        <v>85156.87261904762</v>
+      </c>
+      <c r="Q62" s="4" t="n">
+        <v>26462.85476190476</v>
+      </c>
+      <c r="R62" s="4" t="n"/>
+      <c r="S62" s="4" t="n"/>
+      <c r="T62" s="4" t="n"/>
+      <c r="U62" s="4" t="n"/>
+      <c r="V62" s="4" t="n">
+        <v>93140.40193904762</v>
+      </c>
+      <c r="W62" s="4" t="n">
+        <v>1242036.951939048</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="n">
+        <v>566755.4952380953</v>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>63041.09166666667</v>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>49109.02261904762</v>
+      </c>
+      <c r="E63" s="4" t="n"/>
+      <c r="F63" s="4" t="n">
+        <v>2953.715476190476</v>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>46978.25000000001</v>
+      </c>
+      <c r="H63" s="4" t="n"/>
+      <c r="I63" s="4" t="n">
+        <v>9558.459523809524</v>
+      </c>
+      <c r="J63" s="4" t="n">
+        <v>132408.280952381</v>
+      </c>
+      <c r="K63" s="4" t="n"/>
+      <c r="L63" s="4" t="n"/>
+      <c r="M63" s="4" t="n">
+        <v>23187.96190476191</v>
+      </c>
+      <c r="N63" s="4" t="n"/>
+      <c r="O63" s="4" t="n"/>
+      <c r="P63" s="4" t="n">
+        <v>47011.27619047619</v>
+      </c>
+      <c r="Q63" s="4" t="n">
+        <v>19425.15119047619</v>
+      </c>
+      <c r="R63" s="4" t="n"/>
+      <c r="S63" s="4" t="n"/>
+      <c r="T63" s="4" t="n">
+        <v>42655.43452380953</v>
+      </c>
+      <c r="U63" s="4" t="n"/>
+      <c r="V63" s="4" t="n">
+        <v>70513.66547619048</v>
+      </c>
+      <c r="W63" s="4" t="n">
+        <v>1073597.804761905</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="n">
+        <v>362206.99</v>
+      </c>
+      <c r="C64" s="4" t="n">
+        <v>46617.18095238096</v>
+      </c>
+      <c r="D64" s="4" t="n">
+        <v>133122.3369047619</v>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>18620.38809523809</v>
+      </c>
+      <c r="F64" s="4" t="n"/>
+      <c r="G64" s="4" t="n">
+        <v>92877.49880952382</v>
+      </c>
+      <c r="H64" s="4" t="n"/>
+      <c r="I64" s="4" t="n">
+        <v>73753.77619047619</v>
+      </c>
+      <c r="J64" s="4" t="n">
+        <v>117281.2642857143</v>
+      </c>
+      <c r="K64" s="4" t="n">
+        <v>7068.958333333334</v>
+      </c>
+      <c r="L64" s="4" t="n"/>
+      <c r="M64" s="4" t="n"/>
+      <c r="N64" s="4" t="n"/>
+      <c r="O64" s="4" t="n">
+        <v>50434.89642857143</v>
+      </c>
+      <c r="P64" s="4" t="n">
+        <v>133670.7178571429</v>
+      </c>
+      <c r="Q64" s="4" t="n">
+        <v>43210.71785714286</v>
+      </c>
+      <c r="R64" s="4" t="n"/>
+      <c r="S64" s="4" t="n"/>
+      <c r="T64" s="4" t="n">
+        <v>33757.43214285714</v>
+      </c>
+      <c r="U64" s="4" t="n"/>
+      <c r="V64" s="4" t="n">
+        <v>159564.1972380953</v>
+      </c>
+      <c r="W64" s="4" t="n">
+        <v>1272186.355095238</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="n">
+        <v>325828.0083333334</v>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>135376.0214285714</v>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>114164.5702380952</v>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>65985.65595238096</v>
+      </c>
+      <c r="F65" s="4" t="n"/>
+      <c r="G65" s="4" t="n"/>
+      <c r="H65" s="4" t="n"/>
+      <c r="I65" s="4" t="n">
+        <v>78783.69523809524</v>
+      </c>
+      <c r="J65" s="4" t="n">
+        <v>89229.14047619049</v>
+      </c>
+      <c r="K65" s="4" t="n">
+        <v>54130.83452380952</v>
+      </c>
+      <c r="L65" s="4" t="n"/>
+      <c r="M65" s="4" t="n">
+        <v>21998.77023809524</v>
+      </c>
+      <c r="N65" s="4" t="n"/>
+      <c r="O65" s="4" t="n">
+        <v>47957.92380952382</v>
+      </c>
+      <c r="P65" s="4" t="n">
+        <v>210193.7297619048</v>
+      </c>
+      <c r="Q65" s="4" t="n">
+        <v>37638.27857142857</v>
+      </c>
+      <c r="R65" s="4" t="n"/>
+      <c r="S65" s="4" t="n"/>
+      <c r="T65" s="4" t="n">
+        <v>46855.08095238095</v>
+      </c>
+      <c r="U65" s="4" t="n"/>
+      <c r="V65" s="4" t="n">
+        <v>220995.2476190476</v>
+      </c>
+      <c r="W65" s="4" t="n">
+        <v>1449136.957142857</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="n">
+        <v>490249.5333333334</v>
+      </c>
+      <c r="C66" s="4" t="n">
+        <v>136284.105952381</v>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>54790.05833333333</v>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>18280.67738095238</v>
+      </c>
+      <c r="F66" s="4" t="n"/>
+      <c r="G66" s="4" t="n">
+        <v>84371.73690476191</v>
+      </c>
+      <c r="H66" s="4" t="n"/>
+      <c r="I66" s="4" t="n">
+        <v>77277.96666666667</v>
+      </c>
+      <c r="J66" s="4" t="n">
+        <v>185162.3440476191</v>
+      </c>
+      <c r="K66" s="4" t="n">
+        <v>17214.23333333333</v>
+      </c>
+      <c r="L66" s="4" t="n"/>
+      <c r="M66" s="4" t="n">
+        <v>21486.61547619048</v>
+      </c>
+      <c r="N66" s="4" t="n"/>
+      <c r="O66" s="4" t="n">
+        <v>42497.48571428571</v>
+      </c>
+      <c r="P66" s="4" t="n">
+        <v>77339.27976190476</v>
+      </c>
+      <c r="Q66" s="4" t="n">
+        <v>36337.4630952381</v>
+      </c>
+      <c r="R66" s="4" t="n"/>
+      <c r="S66" s="4" t="n"/>
+      <c r="T66" s="4" t="n">
+        <v>9641.134523809524</v>
+      </c>
+      <c r="U66" s="4" t="n"/>
+      <c r="V66" s="4" t="n">
+        <v>208105.2511904762</v>
+      </c>
+      <c r="W66" s="4" t="n">
+        <v>1459037.885714286</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="n">
+        <v>406775.655952381</v>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>74187.51071428572</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>51543.4119047619</v>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>21802.37380952381</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>2959.05</v>
+      </c>
+      <c r="G67" s="4" t="n">
+        <v>19702.96904761905</v>
+      </c>
+      <c r="H67" s="4" t="n"/>
+      <c r="I67" s="4" t="n">
+        <v>84010.31190476191</v>
+      </c>
+      <c r="J67" s="4" t="n">
+        <v>148536.8595238095</v>
+      </c>
+      <c r="K67" s="4" t="n">
+        <v>22132.58571428571</v>
+      </c>
+      <c r="L67" s="4" t="n"/>
+      <c r="M67" s="4" t="n">
+        <v>24664.53277380953</v>
+      </c>
+      <c r="N67" s="4" t="n"/>
+      <c r="O67" s="4" t="n">
+        <v>42399.87857142858</v>
+      </c>
+      <c r="P67" s="4" t="n">
+        <v>126252.3</v>
+      </c>
+      <c r="Q67" s="4" t="n">
+        <v>27636.12380952381</v>
+      </c>
+      <c r="R67" s="4" t="n">
+        <v>4409.977380952381</v>
+      </c>
+      <c r="S67" s="4" t="n"/>
+      <c r="T67" s="4" t="n">
+        <v>11418.11071428571</v>
+      </c>
+      <c r="U67" s="4" t="n"/>
+      <c r="V67" s="4" t="n">
+        <v>224499.3766428572</v>
+      </c>
+      <c r="W67" s="4" t="n">
+        <v>1292931.028464286</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="n">
+        <v>612398.0928571428</v>
+      </c>
+      <c r="C68" s="4" t="n">
+        <v>94690.38928571428</v>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>55391.36190476191</v>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>62312.1869047619</v>
+      </c>
+      <c r="F68" s="4" t="n"/>
+      <c r="G68" s="4" t="n">
+        <v>206651.1654761905</v>
+      </c>
+      <c r="H68" s="4" t="n"/>
+      <c r="I68" s="4" t="n">
+        <v>54013.94761904762</v>
+      </c>
+      <c r="J68" s="4" t="n">
+        <v>129008.8940476191</v>
+      </c>
+      <c r="K68" s="4" t="n">
+        <v>27696.02261904762</v>
+      </c>
+      <c r="L68" s="4" t="n"/>
+      <c r="M68" s="4" t="n">
+        <v>15504.6130952381</v>
+      </c>
+      <c r="N68" s="4" t="n"/>
+      <c r="O68" s="4" t="n">
+        <v>43492.81904761905</v>
+      </c>
+      <c r="P68" s="4" t="n">
+        <v>136091.219047619</v>
+      </c>
+      <c r="Q68" s="4" t="n">
+        <v>15850.03333333333</v>
+      </c>
+      <c r="R68" s="4" t="n">
+        <v>15189.68333333333</v>
+      </c>
+      <c r="S68" s="4" t="n"/>
+      <c r="T68" s="4" t="n">
+        <v>70335.125</v>
+      </c>
+      <c r="U68" s="4" t="n"/>
+      <c r="V68" s="4" t="n">
+        <v>189320.0130952381</v>
+      </c>
+      <c r="W68" s="4" t="n">
+        <v>1727945.566666667</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="n">
+        <v>289801.5523809524</v>
+      </c>
+      <c r="C69" s="4" t="n">
+        <v>86763.05238095237</v>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>7435.971428571429</v>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>27018.58095238095</v>
+      </c>
+      <c r="F69" s="4" t="n"/>
+      <c r="G69" s="4" t="n">
+        <v>69417.35476190477</v>
+      </c>
+      <c r="H69" s="4" t="n"/>
+      <c r="I69" s="4" t="n">
+        <v>47278.83690476191</v>
+      </c>
+      <c r="J69" s="4" t="n">
+        <v>241357.0226190476</v>
+      </c>
+      <c r="K69" s="4" t="n">
+        <v>30028.16785714286</v>
+      </c>
+      <c r="L69" s="4" t="n"/>
+      <c r="M69" s="4" t="n">
+        <v>21186.93928571428</v>
+      </c>
+      <c r="N69" s="4" t="n"/>
+      <c r="O69" s="4" t="n">
+        <v>25089.18690476191</v>
+      </c>
+      <c r="P69" s="4" t="n">
+        <v>65471.36190476191</v>
+      </c>
+      <c r="Q69" s="4" t="n">
+        <v>26094.46428571429</v>
+      </c>
+      <c r="R69" s="4" t="n">
+        <v>13307.16904761905</v>
+      </c>
+      <c r="S69" s="4" t="n"/>
+      <c r="T69" s="4" t="n">
+        <v>19637.86547619048</v>
+      </c>
+      <c r="U69" s="4" t="n"/>
+      <c r="V69" s="4" t="n">
+        <v>203364.7940476905</v>
+      </c>
+      <c r="W69" s="4" t="n">
+        <v>1173252.320238167</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="n">
+        <v>909605.5701452382</v>
+      </c>
+      <c r="C70" s="4" t="n">
+        <v>84559.39523809525</v>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>20679.55714285714</v>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>20011.25</v>
+      </c>
+      <c r="F70" s="4" t="n"/>
+      <c r="G70" s="4" t="n">
+        <v>156957.3821428572</v>
+      </c>
+      <c r="H70" s="4" t="n"/>
+      <c r="I70" s="4" t="n">
+        <v>38721.45</v>
+      </c>
+      <c r="J70" s="4" t="n">
+        <v>90243.71785714287</v>
+      </c>
+      <c r="K70" s="4" t="n">
+        <v>31870.66071428571</v>
+      </c>
+      <c r="L70" s="4" t="n"/>
+      <c r="M70" s="4" t="n"/>
+      <c r="N70" s="4" t="n"/>
+      <c r="O70" s="4" t="n">
+        <v>26563.82261904762</v>
+      </c>
+      <c r="P70" s="4" t="n">
+        <v>73105.88214285715</v>
+      </c>
+      <c r="Q70" s="4" t="n">
+        <v>12348.15357142857</v>
+      </c>
+      <c r="R70" s="4" t="n">
+        <v>7081.086904761904</v>
+      </c>
+      <c r="S70" s="4" t="n"/>
+      <c r="T70" s="4" t="n">
+        <v>62872.41666666667</v>
+      </c>
+      <c r="U70" s="4" t="n"/>
+      <c r="V70" s="4" t="n">
+        <v>213422.7135369048</v>
+      </c>
+      <c r="W70" s="4" t="n">
+        <v>1748043.058682143</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="n">
+        <v>816819.4821738095</v>
+      </c>
+      <c r="C71" s="4" t="n">
+        <v>154606.8869047619</v>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>83708.98452380953</v>
+      </c>
+      <c r="E71" s="4" t="n">
+        <v>87241.57976190477</v>
+      </c>
+      <c r="F71" s="4" t="n"/>
+      <c r="G71" s="4" t="n">
+        <v>116320.2964285714</v>
+      </c>
+      <c r="H71" s="4" t="n">
+        <v>157.8095238095238</v>
+      </c>
+      <c r="I71" s="4" t="n">
+        <v>20710.28214285714</v>
+      </c>
+      <c r="J71" s="4" t="n"/>
+      <c r="K71" s="4" t="n">
+        <v>17387.29642857143</v>
+      </c>
+      <c r="L71" s="4" t="n"/>
+      <c r="M71" s="4" t="n">
+        <v>21040.2619047619</v>
+      </c>
+      <c r="N71" s="4" t="n"/>
+      <c r="O71" s="4" t="n">
+        <v>29773.17976190476</v>
+      </c>
+      <c r="P71" s="4" t="n">
+        <v>67245.04761904762</v>
+      </c>
+      <c r="Q71" s="4" t="n">
+        <v>39248.4511904762</v>
+      </c>
+      <c r="R71" s="4" t="n"/>
+      <c r="S71" s="4" t="n"/>
+      <c r="T71" s="4" t="n"/>
+      <c r="U71" s="4" t="n"/>
+      <c r="V71" s="4" t="n">
+        <v>145010.0735714286</v>
+      </c>
+      <c r="W71" s="4" t="n">
+        <v>1599269.631935714</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="n">
+        <v>647712.8000785715</v>
+      </c>
+      <c r="C72" s="4" t="n">
+        <v>149851.7404761905</v>
+      </c>
+      <c r="D72" s="4" t="n">
+        <v>112060.525</v>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>79341.2130952381</v>
+      </c>
+      <c r="F72" s="4" t="n"/>
+      <c r="G72" s="4" t="n">
+        <v>90517.3238095238</v>
+      </c>
+      <c r="H72" s="4" t="n">
+        <v>3855.438095238096</v>
+      </c>
+      <c r="I72" s="4" t="n">
+        <v>13786.31547619048</v>
+      </c>
+      <c r="J72" s="4" t="n"/>
+      <c r="K72" s="4" t="n">
+        <v>24539.33333333334</v>
+      </c>
+      <c r="L72" s="4" t="n"/>
+      <c r="M72" s="4" t="n">
+        <v>23955.29761904762</v>
+      </c>
+      <c r="N72" s="4" t="n"/>
+      <c r="O72" s="4" t="n">
+        <v>34424.3</v>
+      </c>
+      <c r="P72" s="4" t="n">
+        <v>44747.34880952381</v>
+      </c>
+      <c r="Q72" s="4" t="n">
+        <v>9029.686904761906</v>
+      </c>
+      <c r="R72" s="4" t="n">
+        <v>26045.975</v>
+      </c>
+      <c r="S72" s="4" t="n"/>
+      <c r="T72" s="4" t="n">
+        <v>3237.203571428572</v>
+      </c>
+      <c r="U72" s="4" t="n"/>
+      <c r="V72" s="4" t="n">
+        <v>102044.9616571429</v>
+      </c>
+      <c r="W72" s="4" t="n">
+        <v>1365149.462926191</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="n">
+        <v>272975.4964285714</v>
+      </c>
+      <c r="C73" s="4" t="n">
+        <v>136269.3583333333</v>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>59248.71666666667</v>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>9944.461904761905</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>27454.69404761905</v>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>130655.9904761905</v>
+      </c>
+      <c r="H73" s="4" t="n"/>
+      <c r="I73" s="4" t="n">
+        <v>68299.98452380951</v>
+      </c>
+      <c r="J73" s="4" t="n"/>
+      <c r="K73" s="4" t="n"/>
+      <c r="L73" s="4" t="n"/>
+      <c r="M73" s="4" t="n">
+        <v>23347.20952380952</v>
+      </c>
+      <c r="N73" s="4" t="n"/>
+      <c r="O73" s="4" t="n">
+        <v>83079.95952380952</v>
+      </c>
+      <c r="P73" s="4" t="n">
+        <v>38406.78452380953</v>
+      </c>
+      <c r="Q73" s="4" t="n">
+        <v>26872.09761904762</v>
+      </c>
+      <c r="R73" s="4" t="n">
+        <v>56246.32261904763</v>
+      </c>
+      <c r="S73" s="4" t="n"/>
+      <c r="T73" s="4" t="n">
+        <v>81001.45119047619</v>
+      </c>
+      <c r="U73" s="4" t="n"/>
+      <c r="V73" s="4" t="n">
+        <v>176448.349143</v>
+      </c>
+      <c r="W73" s="4" t="n">
+        <v>1190250.876523952</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="n">
+        <v>698974.5143904762</v>
+      </c>
+      <c r="C74" s="4" t="n"/>
+      <c r="D74" s="4" t="n">
+        <v>119328.9940476191</v>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>39083.83214285714</v>
+      </c>
+      <c r="F74" s="4" t="n"/>
+      <c r="G74" s="4" t="n">
+        <v>45019.14404761905</v>
+      </c>
+      <c r="H74" s="4" t="n"/>
+      <c r="I74" s="4" t="n">
+        <v>17598.2</v>
+      </c>
+      <c r="J74" s="4" t="n"/>
+      <c r="K74" s="4" t="n">
+        <v>15386.925</v>
+      </c>
+      <c r="L74" s="4" t="n"/>
+      <c r="M74" s="4" t="n">
+        <v>21527.92261904762</v>
+      </c>
+      <c r="N74" s="4" t="n"/>
+      <c r="O74" s="4" t="n">
+        <v>33513.01547619048</v>
+      </c>
+      <c r="P74" s="4" t="n"/>
+      <c r="Q74" s="4" t="n">
+        <v>31851.925</v>
+      </c>
+      <c r="R74" s="4" t="n">
+        <v>35113.8380952381</v>
+      </c>
+      <c r="S74" s="4" t="n">
+        <v>97195.87380952382</v>
+      </c>
+      <c r="T74" s="4" t="n">
+        <v>8876</v>
+      </c>
+      <c r="U74" s="4" t="n"/>
+      <c r="V74" s="4" t="n">
+        <v>159149.4404761905</v>
+      </c>
+      <c r="W74" s="4" t="n">
+        <v>1322619.625104762</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="n">
+        <v>405139.0345238096</v>
+      </c>
+      <c r="C75" s="4" t="n">
+        <v>53721.71785714285</v>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>110709.1989238095</v>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>25653.29761904762</v>
+      </c>
+      <c r="F75" s="4" t="n"/>
+      <c r="G75" s="4" t="n">
+        <v>45504.22738095238</v>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>10375.84761904762</v>
+      </c>
+      <c r="I75" s="4" t="n">
+        <v>31260.2630952381</v>
+      </c>
+      <c r="J75" s="4" t="n"/>
+      <c r="K75" s="4" t="n">
+        <v>44343.62142857143</v>
+      </c>
+      <c r="L75" s="4" t="n"/>
+      <c r="M75" s="4" t="n">
+        <v>23027.08452380952</v>
+      </c>
+      <c r="N75" s="4" t="n"/>
+      <c r="O75" s="4" t="n">
+        <v>51024.54166666666</v>
+      </c>
+      <c r="P75" s="4" t="n">
+        <v>3835.175</v>
+      </c>
+      <c r="Q75" s="4" t="n">
+        <v>32855.7130952381</v>
+      </c>
+      <c r="R75" s="4" t="n">
+        <v>17697.6</v>
+      </c>
+      <c r="S75" s="4" t="n">
+        <v>198512.8214285714</v>
+      </c>
+      <c r="T75" s="4" t="n">
+        <v>37926.12619047619</v>
+      </c>
+      <c r="U75" s="4" t="n"/>
+      <c r="V75" s="4" t="n">
+        <v>289442.7648809524</v>
+      </c>
+      <c r="W75" s="4" t="n">
+        <v>1381029.035233333</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="n">
+        <v>246962.2702380953</v>
+      </c>
+      <c r="C76" s="4" t="n">
+        <v>67224.46547619048</v>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>87902.29880952381</v>
+      </c>
+      <c r="E76" s="4" t="n"/>
+      <c r="F76" s="4" t="n"/>
+      <c r="G76" s="4" t="n">
+        <v>45174.81666666667</v>
+      </c>
+      <c r="H76" s="4" t="n">
+        <v>9770.392857142857</v>
+      </c>
+      <c r="I76" s="4" t="n">
+        <v>45366.28452380952</v>
+      </c>
+      <c r="J76" s="4" t="n"/>
+      <c r="K76" s="4" t="n">
+        <v>69601.65476190476</v>
+      </c>
+      <c r="L76" s="4" t="n"/>
+      <c r="M76" s="4" t="n"/>
+      <c r="N76" s="4" t="n"/>
+      <c r="O76" s="4" t="n">
+        <v>115115.1797619048</v>
+      </c>
+      <c r="P76" s="4" t="n">
+        <v>6395.763095238095</v>
+      </c>
+      <c r="Q76" s="4" t="n">
+        <v>4892.740476190476</v>
+      </c>
+      <c r="R76" s="4" t="n">
+        <v>50709.67857142857</v>
+      </c>
+      <c r="S76" s="4" t="n">
+        <v>84998.54047619046</v>
+      </c>
+      <c r="T76" s="4" t="n">
+        <v>33860.07142857143</v>
+      </c>
+      <c r="U76" s="4" t="n"/>
+      <c r="V76" s="4" t="n">
+        <v>171792.7642857619</v>
+      </c>
+      <c r="W76" s="4" t="n">
+        <v>1039766.921428619</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="n"/>
+      <c r="C77" s="4" t="n">
+        <v>73511.52380952382</v>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>309328.6773809524</v>
+      </c>
+      <c r="E77" s="4" t="n"/>
+      <c r="F77" s="4" t="n"/>
+      <c r="G77" s="4" t="n">
+        <v>178868.9821428572</v>
+      </c>
+      <c r="H77" s="4" t="n"/>
+      <c r="I77" s="4" t="n">
+        <v>13627.86547619048</v>
+      </c>
+      <c r="J77" s="4" t="n"/>
+      <c r="K77" s="4" t="n">
+        <v>168260.8261904762</v>
+      </c>
+      <c r="L77" s="4" t="n"/>
+      <c r="M77" s="4" t="n">
+        <v>38018.51190476191</v>
+      </c>
+      <c r="N77" s="4" t="n"/>
+      <c r="O77" s="4" t="n">
+        <v>69369.97261904762</v>
+      </c>
+      <c r="P77" s="4" t="n"/>
+      <c r="Q77" s="4" t="n"/>
+      <c r="R77" s="4" t="n">
+        <v>79801.6380952381</v>
+      </c>
+      <c r="S77" s="4" t="n">
+        <v>131132.5738095238</v>
+      </c>
+      <c r="T77" s="4" t="n"/>
+      <c r="U77" s="4" t="n"/>
+      <c r="V77" s="4" t="n">
+        <v>127342.4738619048</v>
+      </c>
+      <c r="W77" s="4" t="n">
+        <v>1189263.045290476</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="n"/>
+      <c r="C78" s="4" t="n">
+        <v>54460.44642857143</v>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>318741.6333333334</v>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>47877.12738095238</v>
+      </c>
+      <c r="F78" s="4" t="n"/>
+      <c r="G78" s="4" t="n">
+        <v>191790.2547619048</v>
+      </c>
+      <c r="H78" s="4" t="n"/>
+      <c r="I78" s="4" t="n">
+        <v>30549.66785714286</v>
+      </c>
+      <c r="J78" s="4" t="n"/>
+      <c r="K78" s="4" t="n">
+        <v>79526.79404761904</v>
+      </c>
+      <c r="L78" s="4" t="n"/>
+      <c r="M78" s="4" t="n"/>
+      <c r="N78" s="4" t="n"/>
+      <c r="O78" s="4" t="n">
+        <v>70668.59642857144</v>
+      </c>
+      <c r="P78" s="4" t="n">
+        <v>16837.88928571429</v>
+      </c>
+      <c r="Q78" s="4" t="n"/>
+      <c r="R78" s="4" t="n"/>
+      <c r="S78" s="4" t="n">
+        <v>119301.9654761905</v>
+      </c>
+      <c r="T78" s="4" t="n"/>
+      <c r="U78" s="4" t="n"/>
+      <c r="V78" s="4" t="n">
+        <v>479182.6805726191</v>
+      </c>
+      <c r="W78" s="4" t="n">
+        <v>1408937.055572619</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="n"/>
+      <c r="C79" s="4" t="n">
+        <v>42628.56666666667</v>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>116141.1980952381</v>
+      </c>
+      <c r="E79" s="4" t="n"/>
+      <c r="F79" s="4" t="n"/>
+      <c r="G79" s="4" t="n">
+        <v>36238.06666666667</v>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>15044.34404761905</v>
+      </c>
+      <c r="I79" s="4" t="n">
+        <v>26010.70595238095</v>
+      </c>
+      <c r="J79" s="4" t="n"/>
+      <c r="K79" s="4" t="n">
+        <v>53892.42142857143</v>
+      </c>
+      <c r="L79" s="4" t="n"/>
+      <c r="M79" s="4" t="n">
+        <v>7417.619047619048</v>
+      </c>
+      <c r="N79" s="4" t="n"/>
+      <c r="O79" s="4" t="n">
+        <v>92457.72738095239</v>
+      </c>
+      <c r="P79" s="4" t="n"/>
+      <c r="Q79" s="4" t="n"/>
+      <c r="R79" s="4" t="n"/>
+      <c r="S79" s="4" t="n">
+        <v>70332.25714285715</v>
+      </c>
+      <c r="T79" s="4" t="n"/>
+      <c r="U79" s="4" t="n"/>
+      <c r="V79" s="4" t="n">
+        <v>118080.8135119048</v>
+      </c>
+      <c r="W79" s="4" t="n">
+        <v>578243.7199404762</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="n">
+        <v>562888.2817440477</v>
+      </c>
+      <c r="C80" s="4" t="n">
+        <v>114890.8523809524</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>187786.0714285714</v>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>52350.95476190477</v>
+      </c>
+      <c r="F80" s="4" t="n"/>
+      <c r="G80" s="4" t="n">
+        <v>122177.0345238095</v>
+      </c>
+      <c r="H80" s="4" t="n">
+        <v>9038.760714285714</v>
+      </c>
+      <c r="I80" s="4" t="n">
+        <v>9677.897619047621</v>
+      </c>
+      <c r="J80" s="4" t="n"/>
+      <c r="K80" s="4" t="n">
+        <v>59633.60714285715</v>
+      </c>
+      <c r="L80" s="4" t="n"/>
+      <c r="M80" s="4" t="n"/>
+      <c r="N80" s="4" t="n"/>
+      <c r="O80" s="4" t="n">
+        <v>74778.73571428572</v>
+      </c>
+      <c r="P80" s="4" t="n"/>
+      <c r="Q80" s="4" t="n">
+        <v>20577.79166666667</v>
+      </c>
+      <c r="R80" s="4" t="n"/>
+      <c r="S80" s="4" t="n">
+        <v>112259.7345238095</v>
+      </c>
+      <c r="T80" s="4" t="n"/>
+      <c r="U80" s="4" t="n"/>
+      <c r="V80" s="4" t="n">
+        <v>157575.655047619</v>
+      </c>
+      <c r="W80" s="4" t="n">
+        <v>1483635.377267857</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="n">
+        <v>785008.531702381</v>
+      </c>
+      <c r="C81" s="4" t="n"/>
+      <c r="D81" s="4" t="n">
+        <v>117231.7630952381</v>
+      </c>
+      <c r="E81" s="4" t="n">
+        <v>79929.74523809525</v>
+      </c>
+      <c r="F81" s="4" t="n"/>
+      <c r="G81" s="4" t="n"/>
+      <c r="H81" s="4" t="n"/>
+      <c r="I81" s="4" t="n"/>
+      <c r="J81" s="4" t="n"/>
+      <c r="K81" s="4" t="n">
+        <v>31424.96428571428</v>
+      </c>
+      <c r="L81" s="4" t="n"/>
+      <c r="M81" s="4" t="n">
+        <v>24682.67716666667</v>
+      </c>
+      <c r="N81" s="4" t="n"/>
+      <c r="O81" s="4" t="n">
+        <v>7407.676190476192</v>
+      </c>
+      <c r="P81" s="4" t="n"/>
+      <c r="Q81" s="4" t="n"/>
+      <c r="R81" s="4" t="n"/>
+      <c r="S81" s="4" t="n">
+        <v>42567.85119047619</v>
+      </c>
+      <c r="T81" s="4" t="n"/>
+      <c r="U81" s="4" t="n"/>
+      <c r="V81" s="4" t="n">
+        <v>64785.69058684524</v>
+      </c>
+      <c r="W81" s="4" t="n">
+        <v>1153038.899455893</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:W81"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/dados/oferta-diesel.xlsx
+++ b/dados/oferta-diesel.xlsx
@@ -14,6 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produção por refinaria" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Importação por agente" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Importação por empresa" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Perfil do fornecimento" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Perfil mensal" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Balanço anual'!$A$1:$J$38</definedName>
@@ -22,6 +24,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Produção por refinaria'!$A$1:$W$441</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Importação por agente'!$A$1:$I$81</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Importação por empresa'!$A$1:$W$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Perfil do fornecimento'!$A$1:$I$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Perfil mensal'!$A$1:$I$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -29,8 +33,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -68,7 +73,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -77,6 +82,7 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -442,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -565,258 +571,262 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Perfil do fornecimento</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Quanto do fornecimento veio de cada agente, em janela de 12 meses</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Perfil mensal</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>O mesmo mês a mês, mais ruidoso e sem janela</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>ÓLEO DIESEL E BIODIESEL SÃO PRODUTOS DIFERENTES, e esta planilha nunca soma um no outro.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Óleo diesel A</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>O mineral: o que sai da refinaria ou vem importado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Biodiesel (B100)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Feito de óleo vegetal e gordura animal. Outro produto, e todo nacional.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Óleo diesel B</t>
+          <t>Óleo diesel A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>O que a distribuidora vende: diesel A com biodiesel misturado na proporção que a lei manda (B15 desde 8/2025).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
+          <t>O mineral: o que sai da refinaria ou vem importado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Biodiesel (B100)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Feito de óleo vegetal e gordura animal. Outro produto, e todo nacional.</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O biodiesel entra aqui por uma razão só: sem ele as duas pontas não fecham. A ANP mede VENDAS em diesel B e mede</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>PRODUÇÃO e IMPORTAÇÃO em diesel A. Em 2025 foram 69,5 milhões de m³ vendidos contra 63,7 milhões de oferta de diesel A</t>
-        </is>
-      </c>
-    </row>
+          <t>Óleo diesel B</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>O que a distribuidora vende: diesel A com biodiesel misturado na proporção que a lei manda (B15 desde 8/2025).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>O biodiesel entra aqui por uma razão só: sem ele as duas pontas não fecham. A ANP mede VENDAS em diesel B e mede</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO e IMPORTAÇÃO em diesel A. Em 2025 foram 69,5 milhões de m³ vendidos contra 63,7 milhões de oferta de diesel A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>— o buraco de 5,8 milhões não existe, é biodiesel (9,8 milhões naquele ano). Cada coluna diz qual produto está medindo.</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>As contas:</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>oferta de diesel A</t>
         </is>
       </c>
-      <c r="B23">
+      <c r="B25">
         <f> produção nacional + importação − exportação</f>
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>% importado</t>
         </is>
       </c>
-      <c r="B24">
+      <c r="B26">
         <f> importação ÷ oferta de diesel A</f>
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>diesel A nas vendas</t>
         </is>
       </c>
-      <c r="B25">
+      <c r="B27">
         <f> vendas de diesel B − biodiesel misturado</f>
         <v/>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A produção nacional é de TODAS as refinarias do país, não só as da Petrobras: entram Mataripe (Acelen), Manguinhos</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>(Refit), Riograndense, 3R Potiguar e as demais. Produtores que não são refinaria reportam zero diesel à ANP; a conta</t>
-        </is>
-      </c>
-    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>A produção nacional é de TODAS as refinarias do país, não só as da Petrobras: entram Mataripe (Acelen), Manguinhos</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>(Refit), Riograndense, 3R Potiguar e as demais. Produtores que não são refinaria reportam zero diesel à ANP; a conta</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>os inclui mesmo assim, para o dia em que deixarem de reportar zero.</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>ATENÇÃO — 'vendas' é o que as DISTRIBUIDORAS venderam, não o consumo do país.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Produtor que vende direto a grande consumidor não passa por aí. É essa a maior parte da diferença entre a oferta e as</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>vendas, junto com estoque. Não há dado de estoque aqui, então o resíduo entre as duas não é variação de estoque.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>vendas, junto com estoque. Não há dado de estoque aqui, então o resíduo entre as duas não é variação de estoque.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>O biodiesel misturado só existe na série da ANP a partir de 2017. Antes disso a coluna fica vazia, e 'diesel A nas</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>vendas' também — a mistura existia (B5 desde 2010), mas o volume não está publicado nesse arquivo.</t>
         </is>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>QUEM IMPORTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>A série volumétrica de comércio exterior não diz quem trouxe a carga. Quem diz é o Relatório de Desembaraços, que a</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>ANP monta do Siscomex e publica por empresa. Ele começa em JANEIRO DE 2020 — antes disso não existe dado por agente.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Vem em quilos; a conversão para m³ usa 0,84 t/m³, o mesmo fator que a própria ANP aplica para montar o volumétrico.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42"/>
+          <t>A série volumétrica de comércio exterior não diz quem trouxe a carga. Quem diz é o Relatório de Desembaraços, que a</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ANP monta do Siscomex e publica por empresa. Ele começa em JANEIRO DE 2020 — antes disso não existe dado por agente.</t>
+        </is>
+      </c>
+    </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>importador de registro</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>O relatório nomeia quem registrou a importação, não o dono final da carga. Trading que</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>importa por conta de distribuidora aparece como trading.</t>
-        </is>
-      </c>
-    </row>
+          <t>Vem em quilos; a conversão para m³ usa 0,84 t/m³, o mesmo fator que a própria ANP aplica para montar o volumétrico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>cobertura</t>
-        </is>
-      </c>
-      <c r="B45">
-        <f> desembaraçado ÷ importação volumétrica do mesmo mês. Alguns meses saem incompletos e</f>
-        <v/>
+          <t>importador de registro</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>O relatório nomeia quem registrou a importação, não o dono final da carga. Trading que</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
+          <t>importa por conta de distribuidora aparece como trading.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>cobertura</t>
+        </is>
+      </c>
+      <c r="B47">
+        <f> desembaraçado ÷ importação volumétrica do mesmo mês. Alguns meses saem incompletos e</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>são completados depois; onde a cobertura foge de 100%, a abertura por agente daquele mês não</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>fecha com o total e não deve ser lida como participação.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>classificação</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>O tipo de agente é nosso, feito da razão social mais a estrutura societária conhecida. O</t>
         </is>
       </c>
     </row>
@@ -824,28 +834,48 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
+          <t>fecha com o total e não deve ser lida como participação.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>classificação</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>O tipo de agente é nosso, feito da razão social mais a estrutura societária conhecida. O</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>braço trading de um grupo (Vibra Trading, Royal FIC Comercial) vai com o grupo, não com as</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
         <is>
           <t>tradings independentes. A aba por empresa traz o dado cru, sem classificação.</t>
         </is>
       </c>
     </row>
-    <row r="51"/>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="53"/>
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>A soma móvel de 12 meses existe porque o diesel tem sazonalidade forte (safra, chuva, feriado). Mês contra mês do</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>ano anterior também serve; mês contra mês anterior, não.</t>
         </is>
@@ -56552,4 +56582,5067 @@
   <autoFilter ref="A1:W81"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I70"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>mês</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>âmbito</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Refinarias e Centrais Petroquímicas</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Petrobras</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Outras</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Importações</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Tradings</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Distribuidores</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>volume no período (m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2020-12</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>79.90093643606386</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>78.73826130991627</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>1.162675126147585</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>20.09906356393613</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>18.7554091261486</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>1.343654437787531</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>54226414.45471472</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2021-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>80.74769926268215</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>79.57834241266885</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>1.169356850013286</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>19.25230073731787</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>17.95204085034849</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>1.300259886969372</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>53925833.56866127</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2021-02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>81.30792927170232</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>80.15262421191419</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1.155305059788135</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>18.69207072829769</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>17.40176397607608</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>1.290306752221602</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>53592905.68750584</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2021-03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>81.94450364465094</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>80.81753385835542</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1.126969786295497</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>18.05549635534908</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>16.75328536771786</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>1.302210987631218</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>53916127.87531446</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2021-04</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>82.84368919636353</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>81.75414545217389</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>1.089543744189653</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>17.15631080363647</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>15.96899883009109</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1.18731197354538</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>55085652.62693899</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2021-05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>83.24703215936498</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>82.16732463799823</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>1.079707521366744</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>16.75296784063502</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>15.57261808852395</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>1.180349752111076</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>55908363.10115415</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>83.52483561947638</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>82.51479011737779</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>1.010045502098587</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>16.47516438052362</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>15.23324966904353</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>1.241914711480098</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>56121116.14334038</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>84.17005855470528</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>83.19324152486136</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.976817029843929</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>15.82994144529473</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>14.64711128664019</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.182830158654543</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>56194792.1610242</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>84.53320914294972</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>83.57239113270185</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>0.9608180102478671</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>15.46679085705028</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>14.21209294234518</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1.254697914705103</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>56339088.27961644</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2021-09</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>85.08915865489745</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>84.07634664697716</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>1.01281200792029</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>14.91084134510257</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>13.66592170675428</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1.244919638348291</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>55968533.11050122</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2021-10</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>85.88621887485193</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>84.88959623538295</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>0.996622639468978</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>14.11378112514807</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>12.94655097535798</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1.167230149790081</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>56569610.98090599</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>86.43687401693799</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>85.46212827700755</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.9747457399304369</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>13.56312598306203</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>12.25795465741729</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1.30517132564474</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>56896968.49184372</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>86.29197770875615</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>84.63219072108672</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>1.659786987669421</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>13.70802229124385</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>12.16782073379407</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>1.540201557449786</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>57172757.7380895</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2022-01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>85.82495632097367</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>83.51474777437132</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>2.310208546602357</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>14.17504367902634</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>12.20249486544587</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1.972548813580476</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>58038041.38604188</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2022-02</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>86.01814437696325</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>83.02460530738364</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>2.993539069579612</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>13.98185562303675</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>11.80737881422515</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>2.174476808811605</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>58078943.07479386</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2022-03</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>86.06842803850063</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>82.37825238448782</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>3.6901756540128</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>13.93157196149938</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>11.35889727827357</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>2.572674683225813</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>58681282.33375815</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>85.98907471282946</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>81.68663460984448</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>4.302440102984974</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>14.01092528717054</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>10.82832165822481</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>3.182603628945727</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>59275076.25912732</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2022-05</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>85.62947340405574</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>80.72648646942575</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>4.902986934629998</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>14.37052659594425</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>10.61846336439552</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>3.752063231548728</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>59651225.38263207</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>85.72457137519737</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>80.18319804808753</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>5.541373327109838</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>14.27542862480263</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>10.05751882481786</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>4.217909799984771</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>59826793.33074873</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2022-07</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>85.81979590337303</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>79.61666254964928</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>6.203133353723767</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>14.18020409662696</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>9.298643730512495</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>4.881560366114469</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>60244909.31697486</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>85.88209042900179</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>78.96974318904805</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>6.912347239953752</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>14.1179095709982</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>8.733343071977183</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>5.384566499021019</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>60716421.33271297</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2022-09</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>85.59720767861262</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>78.11050973130065</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>7.486697947311976</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>14.40279232138737</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>8.545901270939799</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>5.85689105044757</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>61799107.11973695</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>85.48402724878626</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>77.24653315772383</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>8.237494091062439</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>14.51597275121375</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>8.014241966556325</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>6.501730784657424</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>61256111.03362522</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>85.52684189834321</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>76.62043624530321</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>8.906405653039995</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>14.47315810165679</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>7.740395455224007</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>6.732762646432787</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>60974321.3553452</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2022-12</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>85.75860679123151</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>76.816904746107</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>8.94170204512452</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>14.24139320876849</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>7.597670736306003</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>6.64372247246249</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>61405548.73222753</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>86.42645342617146</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>77.32010150900273</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>9.106351917168727</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>13.57354657382855</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>7.104918740611145</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>6.468627833217404</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>60692761.922418</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>86.33744846633685</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>77.30199489750382</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>9.035453568833033</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>13.66255153366314</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>7.188574705906562</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>6.473976827756584</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>60973025.07107078</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>85.87271446647981</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>76.7782478280309</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>9.094466638448894</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>14.12728553352021</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>7.715279039848461</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>6.412006493671745</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>61341204.75427315</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>85.7644013691518</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>76.45448032879264</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>9.309921040359161</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>14.2355986308482</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>7.983341252336167</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>6.252257378512032</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>60668892.44577316</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>86.03158424385818</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>76.46851262395656</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>9.563071619901631</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>13.9684157561418</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>8.044416371738805</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>5.923999384402996</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>60796565.38531602</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>85.94390271001335</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>76.11997309262172</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>9.823929617391634</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>14.05609728998664</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>8.405027559177558</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>5.651069730809084</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>61125025.8003422</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>86.22102396973723</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>76.24442422587538</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>9.976599743861865</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>13.77897603026276</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>8.479831209496448</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>5.299144820766316</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>60882891.56761601</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>86.1133306181738</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>75.82460982111679</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>10.288720797057</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>13.88666938182619</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>9.037571560793873</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>4.849097821032311</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>60728339.0960803</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>86.19201925013127</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>75.62370673546032</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>10.56831251467094</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>13.80798074986875</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>9.202683774080519</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>4.605296975788226</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>60271993.7874968</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>85.40681103970606</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>74.71626237819494</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>10.69054866151111</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>14.59318896029394</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>10.3653177932015</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>4.227871167092442</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>60851242.9888478</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>85.26011289636311</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>74.29215412391562</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>10.96795877244749</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>14.73988710363688</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>10.82316305935379</v>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>3.916724044283088</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>61300328.44861548</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>84.13423337601803</v>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>72.85962363106187</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>11.27460974495617</v>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>15.86576662398196</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>11.93082702283989</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>3.934939601142079</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>62129566.32334157</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>83.80807956185116</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>72.27955348974801</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>11.52852607210315</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>16.19192043814884</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>12.15718507875183</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>4.034735359397016</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>62722945.11448442</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>83.9979586203967</v>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>72.19456729490308</v>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>11.80339132549361</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>16.00204137960329</v>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>12.09197757111019</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>3.910063808493098</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>63041936.72691299</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>84.70302075213829</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>72.41692340934195</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>12.28609734279634</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>15.29697924786171</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>11.5503288491233</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>3.746650398738414</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>62777203.62015039</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>85.00242234656405</v>
+      </c>
+      <c r="D42" s="6" t="n">
+        <v>72.44502600227464</v>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>12.5573963442894</v>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>14.99757765343596</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>11.37088586007023</v>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>3.626691793365724</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>63095520.66638848</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>84.5505018407754</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>71.74195851817751</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>12.80854332259788</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>15.4494981592246</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>11.61896343458678</v>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v>3.83053472463782</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>62693462.40157896</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>84.25129032280395</v>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>71.32370017597567</v>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>12.92759014682827</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>15.74870967719605</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>11.47473909735346</v>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>4.273970579842597</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>63157891.4106863</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>83.95456645727359</v>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>70.60801860244693</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>13.34654785482666</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>16.04543354272641</v>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>11.51041790368094</v>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>4.535015639045471</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>63251969.21771011</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>84.37918138809042</v>
+      </c>
+      <c r="D46" s="6" t="n">
+        <v>70.58139186253004</v>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>13.79778952556038</v>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>15.62081861190958</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>10.84934629436125</v>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>4.77147231754833</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>63094102.13665058</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>84.36848768361683</v>
+      </c>
+      <c r="D47" s="6" t="n">
+        <v>70.21181138463574</v>
+      </c>
+      <c r="E47" s="6" t="n">
+        <v>14.1566762989811</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>15.63151231638316</v>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>10.79173110967761</v>
+      </c>
+      <c r="H47" s="6" t="n">
+        <v>4.839781206705546</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>63784849.92428154</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>84.81117466797707</v>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>69.89097821671891</v>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>14.92019645125816</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>15.18882533202293</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>9.98830755341803</v>
+      </c>
+      <c r="H48" s="6" t="n">
+        <v>5.200517778604895</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>63969400.12143528</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>84.83348673037052</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>69.64512843773164</v>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>15.18835829263888</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>15.16651326962947</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>9.628561472093089</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>5.537951797536384</v>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>64008663.51539371</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>86.31571384742226</v>
+      </c>
+      <c r="D50" s="6" t="n">
+        <v>70.66374389416313</v>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>15.65196995325912</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>13.68428615257774</v>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>8.239396740723896</v>
+      </c>
+      <c r="H50" s="6" t="n">
+        <v>5.444889411853848</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>63224227.28153245</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>86.44126935591729</v>
+      </c>
+      <c r="D51" s="6" t="n">
+        <v>70.45319804018193</v>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>15.98807131573535</v>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>13.55873064408273</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>7.929658541809844</v>
+      </c>
+      <c r="H51" s="6" t="n">
+        <v>5.629072102272888</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>63250673.6059953</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>86.63270686444261</v>
+      </c>
+      <c r="D52" s="6" t="n">
+        <v>70.36600207640215</v>
+      </c>
+      <c r="E52" s="6" t="n">
+        <v>16.26670478804046</v>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>13.36729313555739</v>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>7.649171376674719</v>
+      </c>
+      <c r="H52" s="6" t="n">
+        <v>5.718121758882667</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>63251516.86437626</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>86.4685505202858</v>
+      </c>
+      <c r="D53" s="6" t="n">
+        <v>70.1230148834093</v>
+      </c>
+      <c r="E53" s="6" t="n">
+        <v>16.34553563687651</v>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>13.5314494797142</v>
+      </c>
+      <c r="G53" s="6" t="n">
+        <v>7.448864574978573</v>
+      </c>
+      <c r="H53" s="6" t="n">
+        <v>6.082584904735627</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>63355556.82173409</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>85.95351367774811</v>
+      </c>
+      <c r="D54" s="6" t="n">
+        <v>69.70777112809206</v>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>16.24574254965604</v>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>14.04648632225192</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>7.318637427204772</v>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>6.727848895047141</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>63618498.59244837</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="n">
+        <v>86.40896487246921</v>
+      </c>
+      <c r="D55" s="6" t="n">
+        <v>70.07241606644921</v>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>16.33654880602</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>13.59103512753078</v>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>6.740066366904174</v>
+      </c>
+      <c r="H55" s="6" t="n">
+        <v>6.85096876062661</v>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>63865478.62406743</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>86.79692913430374</v>
+      </c>
+      <c r="D56" s="6" t="n">
+        <v>70.20536453446513</v>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>16.5915645998386</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>13.20307086569626</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>6.381442470389963</v>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>6.821628395306294</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>63512588.22328152</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="n">
+        <v>86.8791478846407</v>
+      </c>
+      <c r="D57" s="6" t="n">
+        <v>70.17471707529123</v>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v>16.70443080934946</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>13.1208521153593</v>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v>6.125919693584703</v>
+      </c>
+      <c r="H57" s="6" t="n">
+        <v>6.994932421774596</v>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>64073220.59018628</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>86.97731564199303</v>
+      </c>
+      <c r="D58" s="6" t="n">
+        <v>70.09925206349786</v>
+      </c>
+      <c r="E58" s="6" t="n">
+        <v>16.87806357849517</v>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>13.02268435800698</v>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v>5.888023765896206</v>
+      </c>
+      <c r="H58" s="6" t="n">
+        <v>7.134660592110771</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>64138772.96937682</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>87.5016335804449</v>
+      </c>
+      <c r="D59" s="6" t="n">
+        <v>70.64985076337938</v>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>16.85178281706551</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>12.4983664195551</v>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v>5.217674034468618</v>
+      </c>
+      <c r="H59" s="6" t="n">
+        <v>7.280692385086486</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>64349936.59610659</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>87.87660152103986</v>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>71.58741812645367</v>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>16.28918339458618</v>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>12.12339847896013</v>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>4.921958169972545</v>
+      </c>
+      <c r="H60" s="6" t="n">
+        <v>7.201440308987589</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>63980287.10726832</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>87.99671656190802</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>72.01171961425753</v>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>15.9849969476505</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>12.00328343809198</v>
+      </c>
+      <c r="G61" s="6" t="n">
+        <v>4.951689156015424</v>
+      </c>
+      <c r="H61" s="6" t="n">
+        <v>7.051594282076554</v>
+      </c>
+      <c r="I61" s="4" t="n">
+        <v>64119853.15918268</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>87.5664954424655</v>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>72.12599802035331</v>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>15.44049742211218</v>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>12.43350455753451</v>
+      </c>
+      <c r="G62" s="6" t="n">
+        <v>5.122776731037694</v>
+      </c>
+      <c r="H62" s="6" t="n">
+        <v>7.310727826496812</v>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>63942562.48509046</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="n">
+        <v>87.70158835972073</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>72.83542756562407</v>
+      </c>
+      <c r="E63" s="6" t="n">
+        <v>14.86616079409667</v>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>12.29841164027926</v>
+      </c>
+      <c r="G63" s="6" t="n">
+        <v>5.207039087380746</v>
+      </c>
+      <c r="H63" s="6" t="n">
+        <v>7.091372552898518</v>
+      </c>
+      <c r="I63" s="4" t="n">
+        <v>63892359.40625617</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>86.93888958477115</v>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>72.66399954184472</v>
+      </c>
+      <c r="E64" s="6" t="n">
+        <v>14.27489004292642</v>
+      </c>
+      <c r="F64" s="6" t="n">
+        <v>13.06111041522886</v>
+      </c>
+      <c r="G64" s="6" t="n">
+        <v>5.71162579066069</v>
+      </c>
+      <c r="H64" s="6" t="n">
+        <v>7.349484624568165</v>
+      </c>
+      <c r="I64" s="4" t="n">
+        <v>64395713.20272761</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="n">
+        <v>86.88674397857987</v>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>73.15734883760678</v>
+      </c>
+      <c r="E65" s="6" t="n">
+        <v>13.72939514097311</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>13.11325602142012</v>
+      </c>
+      <c r="G65" s="6" t="n">
+        <v>5.944185189713424</v>
+      </c>
+      <c r="H65" s="6" t="n">
+        <v>7.169070831706696</v>
+      </c>
+      <c r="I65" s="4" t="n">
+        <v>64609363.15606098</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>86.94089147809477</v>
+      </c>
+      <c r="D66" s="6" t="n">
+        <v>73.20952200261044</v>
+      </c>
+      <c r="E66" s="6" t="n">
+        <v>13.73136947548433</v>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>13.05910852190523</v>
+      </c>
+      <c r="G66" s="6" t="n">
+        <v>6.53435571440811</v>
+      </c>
+      <c r="H66" s="6" t="n">
+        <v>6.524752807497117</v>
+      </c>
+      <c r="I66" s="4" t="n">
+        <v>64751640.4052086</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="n">
+        <v>86.40792812380751</v>
+      </c>
+      <c r="D67" s="6" t="n">
+        <v>72.96961462267315</v>
+      </c>
+      <c r="E67" s="6" t="n">
+        <v>13.43831350113436</v>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>13.59207187619249</v>
+      </c>
+      <c r="G67" s="6" t="n">
+        <v>7.019631017189316</v>
+      </c>
+      <c r="H67" s="6" t="n">
+        <v>6.572440859003173</v>
+      </c>
+      <c r="I67" s="4" t="n">
+        <v>65308755.87406693</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="n">
+        <v>86.52435710308005</v>
+      </c>
+      <c r="D68" s="6" t="n">
+        <v>73.49794567070721</v>
+      </c>
+      <c r="E68" s="6" t="n">
+        <v>13.02641143237284</v>
+      </c>
+      <c r="F68" s="6" t="n">
+        <v>13.47564289691995</v>
+      </c>
+      <c r="G68" s="6" t="n">
+        <v>7.239438179387804</v>
+      </c>
+      <c r="H68" s="6" t="n">
+        <v>6.236204717532145</v>
+      </c>
+      <c r="I68" s="4" t="n">
+        <v>64715387.75154312</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="n">
+        <v>86.50338865318925</v>
+      </c>
+      <c r="D69" s="6" t="n">
+        <v>74.06334403463019</v>
+      </c>
+      <c r="E69" s="6" t="n">
+        <v>12.44004461855907</v>
+      </c>
+      <c r="F69" s="6" t="n">
+        <v>13.49661134681073</v>
+      </c>
+      <c r="G69" s="6" t="n">
+        <v>7.698609104221307</v>
+      </c>
+      <c r="H69" s="6" t="n">
+        <v>5.798002242589424</v>
+      </c>
+      <c r="I69" s="4" t="n">
+        <v>64771742.87414432</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="n">
+        <v>86.77426690950951</v>
+      </c>
+      <c r="D70" s="6" t="n">
+        <v>75.12703326923598</v>
+      </c>
+      <c r="E70" s="6" t="n">
+        <v>11.64723364027351</v>
+      </c>
+      <c r="F70" s="6" t="n">
+        <v>13.2257330904905</v>
+      </c>
+      <c r="G70" s="6" t="n">
+        <v>7.709818591463416</v>
+      </c>
+      <c r="H70" s="6" t="n">
+        <v>5.515914499027089</v>
+      </c>
+      <c r="I70" s="4" t="n">
+        <v>64664313.25236204</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I70"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I81"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>mês</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>âmbito</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Refinarias e Centrais Petroquímicas</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Petrobras</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Outras</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Importações</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Tradings</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Distribuidores</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>volume no período (m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2020-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>77.63043401071705</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>76.49993303510477</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>1.130500975612268</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>22.36956598928296</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>20.51098058066352</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>1.858585408619446</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>4594173.744243905</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2020-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>79.47257722740191</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>78.16302132610561</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>1.30955590129631</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>20.52742277259807</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>19.1080095699159</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>1.419413202682164</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>4326005.937703048</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2020-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>77.12234980762183</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>75.93640348511707</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1.185946322504777</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>22.87765019237817</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>21.77477851282668</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>1.102871679551483</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>4134241.834524724</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2020-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>72.58718564044082</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>71.32406011734922</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1.263125523091599</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>27.41281435955917</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>25.49282797734275</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>1.919986382216422</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>3602111.438696774</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2020-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>83.0545097268584</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>81.70643486060911</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>1.34807486624929</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>16.94549027314161</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>16.48158847115872</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.4639018019828909</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>4094439.545642</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2020-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>82.26690681538987</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>80.33422865521815</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>1.932678160171719</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>17.73309318461012</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>17.220077888713</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.5130152958971251</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>4421653.926813762</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2020-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>77.84435321001051</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>76.46833370834186</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>1.376019501668661</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>22.15564678998949</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>21.3314400950564</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>0.8242066949330878</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>4984876.284554332</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2020-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>80.28702615228164</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>79.28227402809371</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>1.004752124187931</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>19.71297384771836</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>19.1722280288725</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.5407458188458644</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>5143323.592312519</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2020-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>80.92462703828916</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>80.41833233175818</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>0.5062947065309756</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>19.07537296171085</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>18.537244794674</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.5381281670368552</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>4848001.308996166</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2020-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>80.65287315453877</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>79.65272268356172</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>1.000150470977055</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>19.34712684546122</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>18.332568392903</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1.014558452558226</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>5164081.288976191</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2020-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>80.93698203468441</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>80.00363318318274</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>0.9333488515016642</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>19.06301796531559</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>16.99987161697501</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>2.063146348340587</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>4418781.479628</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2020-12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>84.7032107501295</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>83.61304520707226</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>1.090165543057239</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>15.29678924987051</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>11.1397663976048</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>4.157022852265712</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>4494724.072623285</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2021-01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>88.10649057107413</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>86.89432218869116</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>1.212168382382967</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>11.89350942892585</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>10.54389377824914</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>1.349615650676711</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>4293592.858190477</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2021-02</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>86.88536253741422</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>85.75271279352077</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>1.132649743893456</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>13.11463746258577</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>11.81887522387355</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1.295762238712215</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>3993078.056547619</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2021-03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>85.12566677595433</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>84.28467717262428</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>0.8409896033300319</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>14.87433322404567</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>13.61388013736585</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>1.260453086679818</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>4457464.022333334</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2021-04</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>85.26121097502455</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>84.4635181400761</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>0.7976928349484441</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>14.73878902497544</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>14.29665856277362</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>0.4421304622018245</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>4771636.19032131</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2021-05</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>87.60527602050355</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>86.41229574686918</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>1.192980273634381</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>12.39472397949645</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>11.88894614759237</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.5057778319040854</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>4917150.019857142</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>85.6760085633094</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>84.62607169016621</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>1.049936873143167</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>14.3239914366906</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>13.03480959027573</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>1.289181846414864</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>4634406.969000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>85.09478413842821</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>84.09322564573337</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1.001558492694832</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>14.9052158615718</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>14.73128792352532</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>0.173927938046483</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>5058552.302238154</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>84.26232708222304</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>83.42880533249433</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.8335217497287063</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>15.73767291777696</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>14.41366083602412</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1.324012081752843</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>5287619.710904762</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2021-09</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>87.57540495606571</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>86.45679650304852</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>1.118608453017185</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>12.42459504393429</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>12.06799991664306</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0.3565951272912304</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>4477446.139880952</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2021-10</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>88.93641542839551</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>88.09380019288156</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>0.8426152355139422</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>11.06358457160449</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>10.78732301881857</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>0.2762615527859236</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>5765159.159380953</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>87.87963124653402</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>87.20417962822339</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>0.6754516183106203</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>12.12036875346598</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>8.465370616844002</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>3.654998136621973</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>4746138.990565739</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>83.06690972391684</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>73.77346224004931</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>9.29344748386751</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>16.93309027608316</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>10.1241900103016</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>6.808900265781554</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>4770513.318869048</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2022-01</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>82.54809526796788</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>73.94352073475213</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>8.604574533215755</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>17.45190473203211</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>11.20635897272797</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>6.245545759304142</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>5158876.506142857</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2022-02</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>89.65602238382448</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>78.6732293081009</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>10.98279307572358</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>10.34397761617551</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>6.134108962385183</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>4.209868653790326</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>4033979.745299608</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2022-03</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>85.81507777522715</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>76.63856783626913</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>9.176509938958018</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>14.18492222477284</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>8.197543418851735</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>5.987378805921105</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>5059803.281297619</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>84.47388288561882</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>76.59203094111093</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>7.881851944507893</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>15.52611711438118</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>8.10995322344349</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>7.416163890937689</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>5365430.115690476</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2022-05</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>83.43800891063293</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>75.25638620535786</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>8.181622705275077</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>16.56199108936709</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>9.448642471978587</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>7.113348617388501</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>5293299.143361904</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>86.85714498941019</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>77.72627556856889</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>9.130869420841311</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>13.14285501058981</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>5.969544890618345</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>7.173310119971469</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>4809974.917116666</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2022-07</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>86.19036211764363</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>77.56266310486228</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>8.627699012781356</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>13.80963788235636</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>6.02662729694491</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>7.783010585411454</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>5476668.288464286</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>85.04658869360657</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>76.29646289893822</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>8.750125794668339</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>14.95341130639344</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>8.035125540624939</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>6.918285765768499</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>5759131.726642858</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2022-09</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>84.07929597253313</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>75.44878670929124</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>8.630509263241878</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>15.92070402746687</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>9.335309090041466</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>6.585394937425401</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>5560131.926904941</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>87.95601398064319</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>78.99738619587851</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>8.958627784764701</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>12.04398601935681</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>4.784006441934261</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>7.259979577422549</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>5222163.073269226</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>88.61560651432315</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>79.28144109052907</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>9.334165423794078</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>11.38439348567685</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>4.753635573802457</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>6.630757911874396</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>4464349.312285715</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2022-12</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>86.00677955173217</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>76.32875094247316</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>9.678028609259</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>13.99322044826783</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>8.241734169351396</v>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>5.751486278916436</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>5201740.69575137</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>91.15004645669775</v>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>80.3519139642564</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>10.79813249244136</v>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>8.84995354330224</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>5.058427632429018</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>3.791525910873222</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>4446089.696333333</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>88.18831855537671</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>78.32942698383707</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>9.85889157153964</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>11.81168144462329</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>7.379481466103536</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>4.432199978519758</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>4314242.893952381</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>80.59858808630904</v>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>70.76474397365261</v>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>9.833844112656413</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>19.40141191369096</v>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>14.08134902787354</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>5.320062885817428</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>5427982.9645</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>82.87330782012972</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>72.37994586121738</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>10.49336195891235</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>17.12669217987027</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>11.63178722137704</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>5.494904958493228</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>4693117.807190476</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>86.48927318992992</v>
+      </c>
+      <c r="D42" s="6" t="n">
+        <v>75.44197645257573</v>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>11.04729673735419</v>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>13.51072681007009</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>10.09909374201384</v>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>3.411633068056243</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>5420972.082904763</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>85.7613444821292</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>73.49977240558826</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>12.26157207654095</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>14.23865551787078</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>10.39187967057636</v>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v>3.846775847294421</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>5138435.332142858</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>89.42496135534549</v>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>79.07688947269642</v>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>10.34807188264907</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>10.57503864465452</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>6.786651086312419</v>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>3.788387558342096</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>5234534.055738095</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>83.84729255722009</v>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>71.7490048893409</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>12.09828766787919</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>16.15270744277991</v>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>14.06624996269914</v>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>2.086457480080771</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>5604579.255107142</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>84.82668195351394</v>
+      </c>
+      <c r="D46" s="6" t="n">
+        <v>73.04266443912572</v>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>11.78401751438823</v>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>15.17331804648604</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>11.31178541487488</v>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>3.861532631611161</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>5103786.618321429</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>79.54380573925371</v>
+      </c>
+      <c r="D47" s="6" t="n">
+        <v>69.14231720414442</v>
+      </c>
+      <c r="E47" s="6" t="n">
+        <v>10.4014885351093</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>20.45619426074628</v>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>17.42010900630575</v>
+      </c>
+      <c r="H47" s="6" t="n">
+        <v>3.036085254440523</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>5801412.27462024</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>86.49210874854681</v>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>73.57298418262963</v>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>12.91912456591718</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>13.5078912514532</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>10.97864750584565</v>
+      </c>
+      <c r="H48" s="6" t="n">
+        <v>2.529243745607543</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>4913434.772053393</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>74.30559876040128</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>61.29117114946756</v>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>13.01442761093374</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>25.6944012395987</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>20.00753626277005</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>5.686864976828657</v>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>6030978.570477452</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>86.26453868325856</v>
+      </c>
+      <c r="D50" s="6" t="n">
+        <v>72.24997346825972</v>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>14.01456521499885</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>13.73546131674143</v>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>8.684956899381859</v>
+      </c>
+      <c r="H50" s="6" t="n">
+        <v>5.050504417359571</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>5039468.487476191</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>90.47032782571817</v>
+      </c>
+      <c r="D51" s="6" t="n">
+        <v>76.75654022213621</v>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>13.71378760358195</v>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>9.529672174281826</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>6.821175991127769</v>
+      </c>
+      <c r="H51" s="6" t="n">
+        <v>2.708496183154056</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>4633234.506380953</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>88.99676835676253</v>
+      </c>
+      <c r="D52" s="6" t="n">
+        <v>73.39494275863031</v>
+      </c>
+      <c r="E52" s="6" t="n">
+        <v>15.60182559813222</v>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>11.00323164323748</v>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>7.597731045616632</v>
+      </c>
+      <c r="H52" s="6" t="n">
+        <v>3.405500597620845</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>5163249.857737405</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>86.75908681839367</v>
+      </c>
+      <c r="D53" s="6" t="n">
+        <v>72.73611497630407</v>
+      </c>
+      <c r="E53" s="6" t="n">
+        <v>14.02297184208959</v>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>13.24091318160634</v>
+      </c>
+      <c r="G53" s="6" t="n">
+        <v>9.367370194201721</v>
+      </c>
+      <c r="H53" s="6" t="n">
+        <v>3.873542987404619</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>5011434.853428571</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>80.96324473571465</v>
+      </c>
+      <c r="D54" s="6" t="n">
+        <v>66.89973250575324</v>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>14.06351222996143</v>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>19.03675526428536</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>13.09605844465787</v>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>5.940696819627492</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>5018913.818095238</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="n">
+        <v>82.2881354547919</v>
+      </c>
+      <c r="D55" s="6" t="n">
+        <v>68.63927729778662</v>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>13.64885815700528</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>17.7118645452081</v>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>8.867835679312416</v>
+      </c>
+      <c r="H55" s="6" t="n">
+        <v>8.844028865895684</v>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>5602864.341250191</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>85.81143180400937</v>
+      </c>
+      <c r="D56" s="6" t="n">
+        <v>70.44468410858552</v>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>15.36674769542386</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>14.18856819599062</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>7.292936750993135</v>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>6.895631444997488</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>5328611.862761904</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="n">
+        <v>88.76287501149399</v>
+      </c>
+      <c r="D57" s="6" t="n">
+        <v>71.47363398202761</v>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v>17.28924102946638</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>11.23712498850603</v>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v>6.482548718481419</v>
+      </c>
+      <c r="H57" s="6" t="n">
+        <v>4.75457627002461</v>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>5446712.174047617</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>84.65562310890797</v>
+      </c>
+      <c r="D58" s="6" t="n">
+        <v>68.68101048492535</v>
+      </c>
+      <c r="E58" s="6" t="n">
+        <v>15.97461262398262</v>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>15.34437689109202</v>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v>10.62244535267574</v>
+      </c>
+      <c r="H58" s="6" t="n">
+        <v>4.721931538416275</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>5794534.405952382</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>84.42335802058828</v>
+      </c>
+      <c r="D59" s="6" t="n">
+        <v>65.7466845010194</v>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>18.67667351956888</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>15.57664197941172</v>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v>8.629911668266921</v>
+      </c>
+      <c r="H59" s="6" t="n">
+        <v>6.946730311144802</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>5985962.471773988</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>86.76714390542377</v>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>70.36643225941503</v>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>16.40071164600873</v>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>13.23285609457621</v>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>6.32143860575465</v>
+      </c>
+      <c r="H60" s="6" t="n">
+        <v>6.911417488821559</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>4952698.166011822</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>90.59331776826275</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>72.31710492172272</v>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>18.27621284654003</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>9.406682231737252</v>
+      </c>
+      <c r="G61" s="6" t="n">
+        <v>4.81901443282321</v>
+      </c>
+      <c r="H61" s="6" t="n">
+        <v>4.587667798914043</v>
+      </c>
+      <c r="I61" s="4" t="n">
+        <v>5246542.336616191</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>87.83243395530884</v>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>69.61291431365913</v>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>18.2195196416497</v>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>12.16756604469117</v>
+      </c>
+      <c r="G62" s="6" t="n">
+        <v>4.815382719976782</v>
+      </c>
+      <c r="H62" s="6" t="n">
+        <v>7.352183324714391</v>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>5065914.811939048</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="n">
+        <v>93.08256609105186</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>75.5652368819929</v>
+      </c>
+      <c r="E63" s="6" t="n">
+        <v>17.51732920905894</v>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>6.917433908948154</v>
+      </c>
+      <c r="G63" s="6" t="n">
+        <v>2.992948494929104</v>
+      </c>
+      <c r="H63" s="6" t="n">
+        <v>3.924485414019049</v>
+      </c>
+      <c r="I63" s="4" t="n">
+        <v>4634077.764761905</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>86.97558216415602</v>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>70.41243746207158</v>
+      </c>
+      <c r="E64" s="6" t="n">
+        <v>16.56314470208445</v>
+      </c>
+      <c r="F64" s="6" t="n">
+        <v>13.02441783584397</v>
+      </c>
+      <c r="G64" s="6" t="n">
+        <v>5.189434264521251</v>
+      </c>
+      <c r="H64" s="6" t="n">
+        <v>7.834983571322717</v>
+      </c>
+      <c r="I64" s="4" t="n">
+        <v>5267289.815095239</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="n">
+        <v>80.53232921060471</v>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>67.59725604374599</v>
+      </c>
+      <c r="E65" s="6" t="n">
+        <v>12.93507316685872</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>19.46767078939529</v>
+      </c>
+      <c r="G65" s="6" t="n">
+        <v>7.700953192094206</v>
+      </c>
+      <c r="H65" s="6" t="n">
+        <v>11.76671759730108</v>
+      </c>
+      <c r="I65" s="4" t="n">
+        <v>5274376.624142857</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>86.72107164738023</v>
+      </c>
+      <c r="D66" s="6" t="n">
+        <v>71.45389817414355</v>
+      </c>
+      <c r="E66" s="6" t="n">
+        <v>15.26717347323668</v>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>13.27892835261978</v>
+      </c>
+      <c r="G66" s="6" t="n">
+        <v>5.808098146753048</v>
+      </c>
+      <c r="H66" s="6" t="n">
+        <v>7.470830205866732</v>
+      </c>
+      <c r="I66" s="4" t="n">
+        <v>5265893.849714285</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="n">
+        <v>86.70461704601682</v>
+      </c>
+      <c r="D67" s="6" t="n">
+        <v>70.15131535351351</v>
+      </c>
+      <c r="E67" s="6" t="n">
+        <v>16.55330169250331</v>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>13.29538295398318</v>
+      </c>
+      <c r="G67" s="6" t="n">
+        <v>4.672336282423571</v>
+      </c>
+      <c r="H67" s="6" t="n">
+        <v>8.62304667155961</v>
+      </c>
+      <c r="I67" s="4" t="n">
+        <v>5249973.940464285</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="n">
+        <v>86.7997626663177</v>
+      </c>
+      <c r="D68" s="6" t="n">
+        <v>70.08846663319261</v>
+      </c>
+      <c r="E68" s="6" t="n">
+        <v>16.71129603312508</v>
+      </c>
+      <c r="F68" s="6" t="n">
+        <v>13.20023733368231</v>
+      </c>
+      <c r="G68" s="6" t="n">
+        <v>4.426154566113252</v>
+      </c>
+      <c r="H68" s="6" t="n">
+        <v>8.774082767569057</v>
+      </c>
+      <c r="I68" s="4" t="n">
+        <v>5889244.229666666</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="n">
+        <v>89.88271906963088</v>
+      </c>
+      <c r="D69" s="6" t="n">
+        <v>70.5801027836273</v>
+      </c>
+      <c r="E69" s="6" t="n">
+        <v>19.30261628600357</v>
+      </c>
+      <c r="F69" s="6" t="n">
+        <v>10.11728093036912</v>
+      </c>
+      <c r="G69" s="6" t="n">
+        <v>3.710234249567725</v>
+      </c>
+      <c r="H69" s="6" t="n">
+        <v>6.4070466808014</v>
+      </c>
+      <c r="I69" s="4" t="n">
+        <v>5512264.553238167</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="n">
+        <v>90.35522420852068</v>
+      </c>
+      <c r="D70" s="6" t="n">
+        <v>74.63043922212557</v>
+      </c>
+      <c r="E70" s="6" t="n">
+        <v>15.72478498639512</v>
+      </c>
+      <c r="F70" s="6" t="n">
+        <v>9.644775791479306</v>
+      </c>
+      <c r="G70" s="6" t="n">
+        <v>3.273307899022743</v>
+      </c>
+      <c r="H70" s="6" t="n">
+        <v>6.371467892456561</v>
+      </c>
+      <c r="I70" s="4" t="n">
+        <v>6005698.032682143</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="n">
+        <v>88.49233949963283</v>
+      </c>
+      <c r="D71" s="6" t="n">
+        <v>76.10461440023941</v>
+      </c>
+      <c r="E71" s="6" t="n">
+        <v>12.38772509939342</v>
+      </c>
+      <c r="F71" s="6" t="n">
+        <v>11.50766050036716</v>
+      </c>
+      <c r="G71" s="6" t="n">
+        <v>5.485739669812145</v>
+      </c>
+      <c r="H71" s="6" t="n">
+        <v>6.021920830555015</v>
+      </c>
+      <c r="I71" s="4" t="n">
+        <v>5616312.982935715</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="n">
+        <v>88.30999421044051</v>
+      </c>
+      <c r="D72" s="6" t="n">
+        <v>75.74253925200541</v>
+      </c>
+      <c r="E72" s="6" t="n">
+        <v>12.56745495843509</v>
+      </c>
+      <c r="F72" s="6" t="n">
+        <v>11.69000578955949</v>
+      </c>
+      <c r="G72" s="6" t="n">
+        <v>6.657443657136375</v>
+      </c>
+      <c r="H72" s="6" t="n">
+        <v>5.032562132423119</v>
+      </c>
+      <c r="I72" s="4" t="n">
+        <v>5092264.21792619</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="n">
+        <v>85.25740441558685</v>
+      </c>
+      <c r="D73" s="6" t="n">
+        <v>73.7692711544463</v>
+      </c>
+      <c r="E73" s="6" t="n">
+        <v>11.48813326114053</v>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v>14.74259558441318</v>
+      </c>
+      <c r="G73" s="6" t="n">
+        <v>6.972439966196583</v>
+      </c>
+      <c r="H73" s="6" t="n">
+        <v>7.770155618216593</v>
+      </c>
+      <c r="I73" s="4" t="n">
+        <v>5069251.662523951</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="n">
+        <v>89.55596924095526</v>
+      </c>
+      <c r="D74" s="6" t="n">
+        <v>78.62478846943948</v>
+      </c>
+      <c r="E74" s="6" t="n">
+        <v>10.9311807715158</v>
+      </c>
+      <c r="F74" s="6" t="n">
+        <v>10.44403075904472</v>
+      </c>
+      <c r="G74" s="6" t="n">
+        <v>5.885677209727044</v>
+      </c>
+      <c r="H74" s="6" t="n">
+        <v>4.558353549317673</v>
+      </c>
+      <c r="I74" s="4" t="n">
+        <v>5015711.733104762</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="n">
+        <v>82.99521669790913</v>
+      </c>
+      <c r="D75" s="6" t="n">
+        <v>73.14899257989606</v>
+      </c>
+      <c r="E75" s="6" t="n">
+        <v>9.846224118013062</v>
+      </c>
+      <c r="F75" s="6" t="n">
+        <v>17.00478330209087</v>
+      </c>
+      <c r="G75" s="6" t="n">
+        <v>9.534678761346354</v>
+      </c>
+      <c r="H75" s="6" t="n">
+        <v>7.470104540744521</v>
+      </c>
+      <c r="I75" s="4" t="n">
+        <v>5137431.561233333</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="n">
+        <v>86.35945903236586</v>
+      </c>
+      <c r="D76" s="6" t="n">
+        <v>76.31581011585003</v>
+      </c>
+      <c r="E76" s="6" t="n">
+        <v>10.04364891651584</v>
+      </c>
+      <c r="F76" s="6" t="n">
+        <v>13.64054096763413</v>
+      </c>
+      <c r="G76" s="6" t="n">
+        <v>7.951201680966314</v>
+      </c>
+      <c r="H76" s="6" t="n">
+        <v>5.689339286667817</v>
+      </c>
+      <c r="I76" s="4" t="n">
+        <v>5480939.768428619</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="n">
+        <v>81.34652708510926</v>
+      </c>
+      <c r="D77" s="6" t="n">
+        <v>68.36698821131061</v>
+      </c>
+      <c r="E77" s="6" t="n">
+        <v>12.97953887379864</v>
+      </c>
+      <c r="F77" s="6" t="n">
+        <v>18.65347291489074</v>
+      </c>
+      <c r="G77" s="6" t="n">
+        <v>14.70981186427512</v>
+      </c>
+      <c r="H77" s="6" t="n">
+        <v>3.943661050615623</v>
+      </c>
+      <c r="I77" s="4" t="n">
+        <v>5416653.873290476</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="n">
+        <v>80.76457962249367</v>
+      </c>
+      <c r="D78" s="6" t="n">
+        <v>68.93115323030102</v>
+      </c>
+      <c r="E78" s="6" t="n">
+        <v>11.83342639219265</v>
+      </c>
+      <c r="F78" s="6" t="n">
+        <v>19.23542037750633</v>
+      </c>
+      <c r="G78" s="6" t="n">
+        <v>11.32025412149839</v>
+      </c>
+      <c r="H78" s="6" t="n">
+        <v>7.915166256007931</v>
+      </c>
+      <c r="I78" s="4" t="n">
+        <v>5823009.318572619</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="n">
+        <v>88.36049958994538</v>
+      </c>
+      <c r="D79" s="6" t="n">
+        <v>77.13469787718917</v>
+      </c>
+      <c r="E79" s="6" t="n">
+        <v>11.2258017127562</v>
+      </c>
+      <c r="F79" s="6" t="n">
+        <v>11.63950041005463</v>
+      </c>
+      <c r="G79" s="6" t="n">
+        <v>7.428012060911267</v>
+      </c>
+      <c r="H79" s="6" t="n">
+        <v>4.211488349143365</v>
+      </c>
+      <c r="I79" s="4" t="n">
+        <v>4656605.817940475</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="n">
+        <v>86.56872060012928</v>
+      </c>
+      <c r="D80" s="6" t="n">
+        <v>76.28026949064639</v>
+      </c>
+      <c r="E80" s="6" t="n">
+        <v>10.28845110948288</v>
+      </c>
+      <c r="F80" s="6" t="n">
+        <v>13.43127939987073</v>
+      </c>
+      <c r="G80" s="6" t="n">
+        <v>9.455057835576229</v>
+      </c>
+      <c r="H80" s="6" t="n">
+        <v>3.976221564294499</v>
+      </c>
+      <c r="I80" s="4" t="n">
+        <v>5945599.352267858</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="n">
+        <v>93.19071956089552</v>
+      </c>
+      <c r="D81" s="6" t="n">
+        <v>83.23701672218395</v>
+      </c>
+      <c r="E81" s="6" t="n">
+        <v>9.953702838711575</v>
+      </c>
+      <c r="F81" s="6" t="n">
+        <v>6.809280439104477</v>
+      </c>
+      <c r="G81" s="6" t="n">
+        <v>3.765071112491273</v>
+      </c>
+      <c r="H81" s="6" t="n">
+        <v>3.044209326613203</v>
+      </c>
+      <c r="I81" s="4" t="n">
+        <v>5404834.931455893</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I81"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>